--- a/data/Величина пм в 4 квартал по субъектам.xlsx
+++ b/data/Величина пм в 4 квартал по субъектам.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\semen\PycharmProjects\Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921EA487-F9A2-47A8-9963-A7952279260F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4703417A-0729-4E55-AB04-C5AF056AD8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -252,9 +252,6 @@
     <t>Еврейская автономная область</t>
   </si>
   <si>
-    <t>Субъект РФ</t>
-  </si>
-  <si>
     <t>Республика Северная Осетия - Алания</t>
   </si>
   <si>
@@ -265,18 +262,29 @@
   </si>
   <si>
     <t>11910.40</t>
+  </si>
+  <si>
+    <t>Регионы</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -313,13 +321,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -601,5456 +615,5659 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W112"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:X112"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.1796875" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1">
+        <v>79</v>
+      </c>
+      <c r="B1" s="3">
+        <v>2001</v>
+      </c>
+      <c r="C1">
         <v>2002</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2003</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2004</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2005</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2006</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2007</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2008</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2009</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2010</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2011</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2012</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2013</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2014</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2015</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2016</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2017</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2018</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2019</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2020</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2021</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2022</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5">
         <v>1576</v>
       </c>
-      <c r="C2">
+      <c r="D2" s="5">
         <v>1714</v>
       </c>
-      <c r="D2">
+      <c r="E2" s="5">
         <v>2019</v>
       </c>
-      <c r="E2">
+      <c r="F2" s="5">
         <v>2369</v>
       </c>
-      <c r="F2">
+      <c r="G2" s="5">
         <v>2901</v>
       </c>
-      <c r="G2">
+      <c r="H2" s="5">
         <v>3306</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="5">
         <v>3839</v>
       </c>
-      <c r="I2">
+      <c r="J2" s="5">
         <v>4172</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="5">
         <v>4777</v>
       </c>
-      <c r="K2">
+      <c r="L2" s="5">
         <v>4959</v>
       </c>
-      <c r="L2">
+      <c r="M2" s="5">
         <v>5256</v>
       </c>
-      <c r="M2">
+      <c r="N2" s="5">
         <v>6106</v>
       </c>
-      <c r="N2">
+      <c r="O2" s="5">
         <v>6842</v>
       </c>
-      <c r="O2">
+      <c r="P2" s="5">
         <v>7918</v>
       </c>
-      <c r="P2">
+      <c r="Q2" s="5">
         <v>8099</v>
       </c>
-      <c r="Q2">
+      <c r="R2" s="5">
         <v>8281</v>
       </c>
-      <c r="R2">
+      <c r="S2" s="5">
         <v>8480</v>
       </c>
-      <c r="S2">
+      <c r="T2" s="5">
         <v>9236</v>
       </c>
-      <c r="T2">
+      <c r="U2" s="5">
         <v>9593</v>
       </c>
-      <c r="U2">
+      <c r="V2" s="5">
         <v>9720</v>
       </c>
-      <c r="V2">
+      <c r="W2" s="5">
         <v>11692</v>
       </c>
-      <c r="W2">
+      <c r="X2" s="5">
         <v>12075</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
+        <v>1258</v>
+      </c>
+      <c r="C3" s="5">
         <v>1540</v>
       </c>
-      <c r="C3">
+      <c r="D3" s="5">
         <v>1757</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="5">
         <v>2000</v>
       </c>
-      <c r="E3">
+      <c r="F3" s="5">
         <v>2342</v>
       </c>
-      <c r="F3">
+      <c r="G3" s="5">
         <v>2873</v>
       </c>
-      <c r="G3">
+      <c r="H3" s="5">
         <v>3405</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="5">
         <v>3983</v>
       </c>
-      <c r="I3">
+      <c r="J3" s="5">
         <v>4311</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="5">
         <v>4933</v>
       </c>
-      <c r="K3">
+      <c r="L3" s="5">
         <v>5128</v>
       </c>
-      <c r="L3">
+      <c r="M3" s="5">
         <v>5423</v>
       </c>
-      <c r="M3">
+      <c r="N3" s="5">
         <v>6543</v>
       </c>
-      <c r="N3">
+      <c r="O3" s="5">
         <v>7565</v>
       </c>
-      <c r="O3">
+      <c r="P3" s="5">
         <v>8723</v>
       </c>
-      <c r="P3">
+      <c r="Q3" s="5">
         <v>8971</v>
       </c>
-      <c r="Q3">
+      <c r="R3" s="5">
         <v>9279</v>
       </c>
-      <c r="R3">
+      <c r="S3" s="5">
         <v>9655</v>
       </c>
-      <c r="S3">
+      <c r="T3" s="5">
         <v>10320</v>
       </c>
-      <c r="T3">
+      <c r="U3" s="5">
         <v>10950</v>
       </c>
-      <c r="U3">
+      <c r="V3" s="5">
         <v>11280</v>
       </c>
-      <c r="V3">
+      <c r="W3" s="5">
         <v>13127</v>
       </c>
-      <c r="W3">
+      <c r="X3" s="5">
         <v>13560</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="6">
+        <v>1328</v>
+      </c>
+      <c r="C4" s="5">
         <v>1546</v>
       </c>
-      <c r="C4">
+      <c r="D4" s="5">
         <v>1857</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="5">
         <v>2177</v>
       </c>
-      <c r="E4">
+      <c r="F4" s="5">
         <v>2595</v>
       </c>
-      <c r="F4">
+      <c r="G4" s="5">
         <v>3222</v>
       </c>
-      <c r="G4">
+      <c r="H4" s="5">
         <v>3777</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="5">
         <v>4545</v>
       </c>
-      <c r="I4">
+      <c r="J4" s="5">
         <v>4973</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="5">
         <v>5774</v>
       </c>
-      <c r="K4">
+      <c r="L4" s="5">
         <v>5983</v>
       </c>
-      <c r="L4">
+      <c r="M4" s="5">
         <v>6419</v>
       </c>
-      <c r="M4">
+      <c r="N4" s="5">
         <v>6989</v>
       </c>
-      <c r="N4">
+      <c r="O4" s="5">
         <v>7954</v>
       </c>
-      <c r="O4">
+      <c r="P4" s="5">
         <v>8908</v>
       </c>
-      <c r="P4">
+      <c r="Q4" s="5">
         <v>9092</v>
       </c>
-      <c r="Q4">
+      <c r="R4" s="5">
         <v>9104</v>
       </c>
-      <c r="R4">
+      <c r="S4" s="5">
         <v>9523</v>
       </c>
-      <c r="S4">
+      <c r="T4" s="5">
         <v>9901</v>
       </c>
-      <c r="T4">
+      <c r="U4" s="5">
         <v>10808</v>
       </c>
-      <c r="U4">
+      <c r="V4" s="5">
         <v>11093</v>
       </c>
-      <c r="V4">
+      <c r="W4" s="5">
         <v>13501</v>
       </c>
-      <c r="W4">
+      <c r="X4" s="5">
         <v>13944</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5">
         <v>1693</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="5">
         <v>1810</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="5">
         <v>2109</v>
       </c>
-      <c r="E5">
+      <c r="F5" s="5">
         <v>2485</v>
       </c>
-      <c r="F5">
+      <c r="G5" s="5">
         <v>2813</v>
       </c>
-      <c r="G5">
+      <c r="H5" s="5">
         <v>3607</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="5">
         <v>4180</v>
       </c>
-      <c r="I5">
+      <c r="J5" s="5">
         <v>4924</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="5">
         <v>5594</v>
       </c>
-      <c r="K5">
+      <c r="L5" s="5">
         <v>5662</v>
       </c>
-      <c r="L5">
+      <c r="M5" s="5">
         <v>5756</v>
       </c>
-      <c r="M5">
+      <c r="N5" s="5">
         <v>6043</v>
       </c>
-      <c r="N5">
+      <c r="O5" s="5">
         <v>7026</v>
       </c>
-      <c r="O5">
+      <c r="P5" s="5">
         <v>7884</v>
       </c>
-      <c r="P5">
+      <c r="Q5" s="5">
         <v>8121</v>
       </c>
-      <c r="Q5">
+      <c r="R5" s="5">
         <v>8034</v>
       </c>
-      <c r="R5">
+      <c r="S5" s="5">
         <v>8612</v>
       </c>
-      <c r="S5">
+      <c r="T5" s="5">
         <v>8894</v>
       </c>
-      <c r="T5">
+      <c r="U5" s="5">
         <v>9053</v>
       </c>
-      <c r="U5">
+      <c r="V5" s="5">
         <v>9747</v>
       </c>
-      <c r="V5">
+      <c r="W5" s="5">
         <v>11832</v>
       </c>
-      <c r="W5">
+      <c r="X5" s="5">
         <v>12363</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="6">
+        <v>1497</v>
+      </c>
+      <c r="C6" s="5">
         <v>1848</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="5">
         <v>2065</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="5">
         <v>2365</v>
       </c>
-      <c r="E6">
+      <c r="F6" s="5">
         <v>2599</v>
       </c>
-      <c r="F6">
+      <c r="G6" s="5">
         <v>3090</v>
       </c>
-      <c r="G6">
+      <c r="H6" s="5">
         <v>3707</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="5">
         <v>4252</v>
       </c>
-      <c r="I6">
+      <c r="J6" s="5">
         <v>4642</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="5">
         <v>5440</v>
       </c>
-      <c r="K6">
+      <c r="L6" s="5">
         <v>5738</v>
       </c>
-      <c r="L6">
+      <c r="M6" s="5">
         <v>6206</v>
       </c>
-      <c r="M6">
+      <c r="N6" s="5">
         <v>7036</v>
       </c>
-      <c r="N6">
+      <c r="O6" s="5">
         <v>8170</v>
       </c>
-      <c r="O6">
+      <c r="P6" s="5">
         <v>9041</v>
       </c>
-      <c r="P6">
+      <c r="Q6" s="5">
         <v>9373</v>
       </c>
-      <c r="Q6">
+      <c r="R6" s="5">
         <v>9488</v>
       </c>
-      <c r="R6">
+      <c r="S6" s="5">
         <v>9900</v>
       </c>
-      <c r="S6">
+      <c r="T6" s="5">
         <v>9839</v>
       </c>
-      <c r="T6">
+      <c r="U6" s="5">
         <v>10581</v>
       </c>
-      <c r="U6">
+      <c r="V6" s="5">
         <v>10761</v>
       </c>
-      <c r="V6">
+      <c r="W6" s="5">
         <v>12806</v>
       </c>
-      <c r="W6">
+      <c r="X6" s="5">
         <v>13369</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="6">
+        <v>1359</v>
+      </c>
+      <c r="C7" s="5">
         <v>1771</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="5">
         <v>2066</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="5">
         <v>2307</v>
       </c>
-      <c r="E7">
+      <c r="F7" s="5">
         <v>2668</v>
       </c>
-      <c r="F7">
+      <c r="G7" s="5">
         <v>3197</v>
       </c>
-      <c r="G7">
+      <c r="H7" s="5">
         <v>3600</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="5">
         <v>4234</v>
       </c>
-      <c r="I7">
+      <c r="J7" s="5">
         <v>4583</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="5">
         <v>5256</v>
       </c>
-      <c r="K7">
+      <c r="L7" s="5">
         <v>5412</v>
       </c>
-      <c r="L7">
+      <c r="M7" s="5">
         <v>5757</v>
       </c>
-      <c r="M7">
+      <c r="N7" s="5">
         <v>6682</v>
       </c>
-      <c r="N7">
+      <c r="O7" s="5">
         <v>7704</v>
       </c>
-      <c r="O7">
+      <c r="P7" s="5">
         <v>8958</v>
       </c>
-      <c r="P7">
+      <c r="Q7" s="5">
         <v>9349</v>
       </c>
-      <c r="Q7">
+      <c r="R7" s="5">
         <v>9601</v>
       </c>
-      <c r="R7">
+      <c r="S7" s="5">
         <v>10240</v>
       </c>
-      <c r="S7">
+      <c r="T7" s="5">
         <v>10565</v>
       </c>
-      <c r="T7">
+      <c r="U7" s="5">
         <v>10964</v>
       </c>
-      <c r="U7">
+      <c r="V7" s="5">
         <v>11618</v>
       </c>
-      <c r="V7">
+      <c r="W7" s="5">
         <v>13363</v>
       </c>
-      <c r="W7">
+      <c r="X7" s="5">
         <v>13800</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="6">
+        <v>1386</v>
+      </c>
+      <c r="C8" s="5">
         <v>1701</v>
       </c>
-      <c r="C8">
+      <c r="D8" s="5">
         <v>1952</v>
       </c>
-      <c r="D8">
+      <c r="E8" s="5">
         <v>2212</v>
       </c>
-      <c r="E8">
+      <c r="F8" s="5">
         <v>2579</v>
       </c>
-      <c r="F8">
+      <c r="G8" s="5">
         <v>2952</v>
       </c>
-      <c r="G8">
+      <c r="H8" s="5">
         <v>3637</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="5">
         <v>4323</v>
       </c>
-      <c r="I8">
+      <c r="J8" s="5">
         <v>4789</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="5">
         <v>5668</v>
       </c>
-      <c r="K8">
+      <c r="L8" s="5">
         <v>5962</v>
       </c>
-      <c r="L8">
+      <c r="M8" s="5">
         <v>6547</v>
       </c>
-      <c r="M8">
+      <c r="N8" s="5">
         <v>6916</v>
       </c>
-      <c r="N8">
+      <c r="O8" s="5">
         <v>7668</v>
       </c>
-      <c r="O8">
+      <c r="P8" s="5">
         <v>8742</v>
       </c>
-      <c r="P8">
+      <c r="Q8" s="5">
         <v>9195</v>
       </c>
-      <c r="Q8">
+      <c r="R8" s="5">
         <v>9291</v>
       </c>
-      <c r="R8">
+      <c r="S8" s="5">
         <v>9664</v>
       </c>
-      <c r="S8">
+      <c r="T8" s="5">
         <v>10128</v>
       </c>
-      <c r="T8">
+      <c r="U8" s="5">
         <v>11010</v>
       </c>
-      <c r="U8">
+      <c r="V8" s="5">
         <v>11241</v>
       </c>
-      <c r="V8">
+      <c r="W8" s="5">
         <v>12860</v>
       </c>
-      <c r="W8">
+      <c r="X8" s="5">
         <v>13284</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="6">
+        <v>1456</v>
+      </c>
+      <c r="C9" s="5">
         <v>1762</v>
       </c>
-      <c r="C9">
+      <c r="D9" s="5">
         <v>2164</v>
       </c>
-      <c r="D9">
+      <c r="E9" s="5">
         <v>2334</v>
       </c>
-      <c r="E9">
+      <c r="F9" s="5">
         <v>2535</v>
       </c>
-      <c r="F9">
+      <c r="G9" s="5">
         <v>2849</v>
       </c>
-      <c r="G9">
+      <c r="H9" s="5">
         <v>3422</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="5">
         <v>4042</v>
       </c>
-      <c r="I9">
+      <c r="J9" s="5">
         <v>4493</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="5">
         <v>5120</v>
       </c>
-      <c r="K9">
+      <c r="L9" s="5">
         <v>5180</v>
       </c>
-      <c r="L9">
+      <c r="M9" s="5">
         <v>5456</v>
       </c>
-      <c r="M9">
+      <c r="N9" s="5">
         <v>5925</v>
       </c>
-      <c r="N9">
+      <c r="O9" s="5">
         <v>6754</v>
       </c>
-      <c r="O9">
+      <c r="P9" s="5">
         <v>7916</v>
       </c>
-      <c r="P9">
+      <c r="Q9" s="5">
         <v>8258</v>
       </c>
-      <c r="Q9">
+      <c r="R9" s="5">
         <v>8476</v>
       </c>
-      <c r="R9">
+      <c r="S9" s="5">
         <v>9058</v>
       </c>
-      <c r="S9">
+      <c r="T9" s="5">
         <v>9449</v>
       </c>
-      <c r="T9">
+      <c r="U9" s="5">
         <v>9997</v>
       </c>
-      <c r="U9">
+      <c r="V9" s="5">
         <v>10459</v>
       </c>
-      <c r="V9">
+      <c r="W9" s="5">
         <v>12110</v>
       </c>
-      <c r="W9">
+      <c r="X9" s="5">
         <v>12506</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="6">
+        <v>1254</v>
+      </c>
+      <c r="C10" s="5">
         <v>1480</v>
       </c>
-      <c r="C10">
+      <c r="D10" s="5">
         <v>1703</v>
       </c>
-      <c r="D10">
+      <c r="E10" s="5">
         <v>1963</v>
       </c>
-      <c r="E10">
+      <c r="F10" s="5">
         <v>2369</v>
       </c>
-      <c r="F10">
+      <c r="G10" s="5">
         <v>2721</v>
       </c>
-      <c r="G10">
+      <c r="H10" s="5">
         <v>3394</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="5">
         <v>4137</v>
       </c>
-      <c r="I10">
+      <c r="J10" s="5">
         <v>4563</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="5">
         <v>5276</v>
       </c>
-      <c r="K10">
+      <c r="L10" s="5">
         <v>5356</v>
       </c>
-      <c r="L10">
+      <c r="M10" s="5">
         <v>5724</v>
       </c>
-      <c r="M10">
+      <c r="N10" s="5">
         <v>6215</v>
       </c>
-      <c r="N10">
+      <c r="O10" s="5">
         <v>7062</v>
       </c>
-      <c r="O10">
+      <c r="P10" s="5">
         <v>8008</v>
       </c>
-      <c r="P10">
+      <c r="Q10" s="5">
         <v>8313</v>
       </c>
-      <c r="Q10">
+      <c r="R10" s="5">
         <v>8313</v>
       </c>
-      <c r="R10">
+      <c r="S10" s="5">
         <v>8720</v>
       </c>
-      <c r="S10">
+      <c r="T10" s="5">
         <v>9169</v>
       </c>
-      <c r="T10">
+      <c r="U10" s="5">
         <v>9828</v>
       </c>
-      <c r="U10">
+      <c r="V10" s="5">
         <v>9945</v>
       </c>
-      <c r="V10">
+      <c r="W10" s="5">
         <v>11553</v>
       </c>
-      <c r="W10">
+      <c r="X10" s="5">
         <v>11931</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="6">
+        <v>1653</v>
+      </c>
+      <c r="C11" s="5">
         <v>2115</v>
       </c>
-      <c r="C11">
+      <c r="D11" s="5">
         <v>2380</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="5">
         <v>2817</v>
       </c>
-      <c r="E11">
+      <c r="F11" s="5">
         <v>3227</v>
       </c>
-      <c r="F11">
+      <c r="G11" s="5">
         <v>3775</v>
       </c>
-      <c r="G11">
+      <c r="H11" s="5">
         <v>4467</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="5">
         <v>5170</v>
       </c>
-      <c r="I11">
+      <c r="J11" s="5">
         <v>5850</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="5">
         <v>6585</v>
       </c>
-      <c r="K11">
+      <c r="L11" s="5">
         <v>6801</v>
       </c>
-      <c r="L11">
+      <c r="M11" s="5">
         <v>7223</v>
       </c>
-      <c r="M11">
+      <c r="N11" s="5">
         <v>8072</v>
       </c>
-      <c r="N11">
+      <c r="O11" s="5">
         <v>9150</v>
       </c>
-      <c r="O11">
+      <c r="P11" s="5">
         <v>10460</v>
       </c>
-      <c r="P11">
+      <c r="Q11" s="5">
         <v>11021</v>
       </c>
-      <c r="Q11">
+      <c r="R11" s="5">
         <v>11365</v>
       </c>
-      <c r="R11">
+      <c r="S11" s="5">
         <v>11764</v>
       </c>
-      <c r="S11">
+      <c r="T11" s="5">
         <v>12272</v>
       </c>
-      <c r="T11">
+      <c r="U11" s="5">
         <v>13169</v>
       </c>
-      <c r="U11">
+      <c r="V11" s="5">
         <v>13580</v>
       </c>
-      <c r="V11">
+      <c r="W11" s="5">
         <v>16223</v>
       </c>
-      <c r="W11">
+      <c r="X11" s="5">
         <v>17277</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="C12">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5">
         <v>1728</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="5">
         <v>1980</v>
       </c>
-      <c r="E12">
+      <c r="F12" s="5">
         <v>2333</v>
       </c>
-      <c r="F12">
+      <c r="G12" s="5">
         <v>2629</v>
       </c>
-      <c r="G12">
+      <c r="H12" s="5">
         <v>3176</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="5">
         <v>3743</v>
       </c>
-      <c r="I12">
+      <c r="J12" s="5">
         <v>4145</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="5">
         <v>4813</v>
       </c>
-      <c r="K12">
+      <c r="L12" s="5">
         <v>4966</v>
       </c>
-      <c r="L12">
+      <c r="M12" s="5">
         <v>5236</v>
       </c>
-      <c r="M12">
+      <c r="N12" s="5">
         <v>6443</v>
       </c>
-      <c r="N12">
+      <c r="O12" s="5">
         <v>7334</v>
       </c>
-      <c r="O12">
+      <c r="P12" s="5">
         <v>8419</v>
       </c>
-      <c r="P12">
+      <c r="Q12" s="5">
         <v>8739</v>
       </c>
-      <c r="Q12">
+      <c r="R12" s="5">
         <v>8932</v>
       </c>
-      <c r="R12">
+      <c r="S12" s="5">
         <v>9513</v>
       </c>
-      <c r="S12">
+      <c r="T12" s="5">
         <v>9810</v>
       </c>
-      <c r="T12">
+      <c r="U12" s="5">
         <v>10378</v>
       </c>
-      <c r="U12">
+      <c r="V12" s="5">
         <v>10722</v>
       </c>
-      <c r="V12">
+      <c r="W12" s="5">
         <v>12945</v>
       </c>
-      <c r="W12">
+      <c r="X12" s="5">
         <v>13369</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="6">
+        <v>1382</v>
+      </c>
+      <c r="C13" s="5">
         <v>1629</v>
       </c>
-      <c r="C13">
+      <c r="D13" s="5">
         <v>1918</v>
       </c>
-      <c r="D13">
+      <c r="E13" s="5">
         <v>2192</v>
       </c>
-      <c r="E13">
+      <c r="F13" s="5">
         <v>2495</v>
       </c>
-      <c r="F13">
+      <c r="G13" s="5">
         <v>2966</v>
       </c>
-      <c r="G13">
+      <c r="H13" s="5">
         <v>3686</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="5">
         <v>4383</v>
       </c>
-      <c r="I13">
+      <c r="J13" s="5">
         <v>4868</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="5">
         <v>5669</v>
       </c>
-      <c r="K13">
+      <c r="L13" s="5">
         <v>5901</v>
       </c>
-      <c r="L13">
+      <c r="M13" s="5">
         <v>6340</v>
       </c>
-      <c r="M13">
+      <c r="N13" s="5">
         <v>6677</v>
       </c>
-      <c r="N13">
+      <c r="O13" s="5">
         <v>7172</v>
       </c>
-      <c r="O13">
+      <c r="P13" s="5">
         <v>8450</v>
       </c>
-      <c r="P13">
+      <c r="Q13" s="5">
         <v>8658</v>
       </c>
-      <c r="Q13">
+      <c r="R13" s="5">
         <v>8898</v>
       </c>
-      <c r="R13">
+      <c r="S13" s="5">
         <v>9474</v>
       </c>
-      <c r="S13">
+      <c r="T13" s="5">
         <v>9615</v>
       </c>
-      <c r="T13">
+      <c r="U13" s="5">
         <v>10785</v>
       </c>
-      <c r="U13">
+      <c r="V13" s="5">
         <v>10785</v>
       </c>
-      <c r="V13">
+      <c r="W13" s="5">
         <v>12388</v>
       </c>
-      <c r="W13">
+      <c r="X13" s="5">
         <v>12794</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="6">
+        <v>1380</v>
+      </c>
+      <c r="C14" s="5">
         <v>1694</v>
       </c>
-      <c r="C14">
+      <c r="D14" s="5">
         <v>1925</v>
       </c>
-      <c r="D14">
+      <c r="E14" s="5">
         <v>2165</v>
       </c>
-      <c r="E14">
+      <c r="F14" s="5">
         <v>2510</v>
       </c>
-      <c r="F14">
+      <c r="G14" s="5">
         <v>3187</v>
       </c>
-      <c r="G14">
+      <c r="H14" s="5">
         <v>3723</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="5">
         <v>4474</v>
       </c>
-      <c r="I14">
+      <c r="J14" s="5">
         <v>4977</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="5">
         <v>5817</v>
       </c>
-      <c r="K14">
+      <c r="L14" s="5">
         <v>6574</v>
       </c>
-      <c r="L14">
+      <c r="M14" s="5">
         <v>7199</v>
       </c>
-      <c r="M14">
+      <c r="N14" s="5">
         <v>7663</v>
       </c>
-      <c r="N14">
+      <c r="O14" s="5">
         <v>8695</v>
       </c>
-      <c r="O14">
+      <c r="P14" s="5">
         <v>9918</v>
       </c>
-      <c r="P14">
+      <c r="Q14" s="5">
         <v>10074</v>
       </c>
-      <c r="Q14">
+      <c r="R14" s="5">
         <v>9664</v>
       </c>
-      <c r="R14">
+      <c r="S14" s="5">
         <v>10148</v>
       </c>
-      <c r="S14">
+      <c r="T14" s="5">
         <v>10330</v>
       </c>
-      <c r="T14">
+      <c r="U14" s="5">
         <v>10752</v>
       </c>
-      <c r="U14">
+      <c r="V14" s="5">
         <v>11201</v>
       </c>
-      <c r="V14">
+      <c r="W14" s="5">
         <v>13363</v>
       </c>
-      <c r="W14">
+      <c r="X14" s="5">
         <v>13944</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="6">
+        <v>1302</v>
+      </c>
+      <c r="C15" s="5">
         <v>1509</v>
       </c>
-      <c r="C15">
+      <c r="D15" s="5">
         <v>1683</v>
       </c>
-      <c r="D15">
+      <c r="E15" s="5">
         <v>2016</v>
       </c>
-      <c r="E15">
+      <c r="F15" s="5">
         <v>2303</v>
       </c>
-      <c r="F15">
+      <c r="G15" s="5">
         <v>2736</v>
       </c>
-      <c r="G15">
+      <c r="H15" s="5">
         <v>3076</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="5">
         <v>3493</v>
       </c>
-      <c r="I15">
+      <c r="J15" s="5">
         <v>3805</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="5">
         <v>4199</v>
       </c>
-      <c r="K15">
+      <c r="L15" s="5">
         <v>4593</v>
       </c>
-      <c r="L15">
+      <c r="M15" s="5">
         <v>4870</v>
       </c>
-      <c r="M15">
+      <c r="N15" s="5">
         <v>5230</v>
       </c>
-      <c r="N15">
+      <c r="O15" s="5">
         <v>6850</v>
       </c>
-      <c r="O15">
+      <c r="P15" s="5">
         <v>7834</v>
       </c>
-      <c r="P15">
+      <c r="Q15" s="5">
         <v>8268</v>
       </c>
-      <c r="Q15">
+      <c r="R15" s="5">
         <v>8214</v>
       </c>
-      <c r="R15">
+      <c r="S15" s="5">
         <v>8722</v>
       </c>
-      <c r="S15">
+      <c r="T15" s="5">
         <v>9805</v>
       </c>
-      <c r="T15">
+      <c r="U15" s="5">
         <v>10178</v>
       </c>
-      <c r="U15">
+      <c r="V15" s="5">
         <v>10221</v>
       </c>
-      <c r="V15">
+      <c r="W15" s="5">
         <v>12210</v>
       </c>
-      <c r="W15">
+      <c r="X15" s="5">
         <v>12796</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="6">
+        <v>1443</v>
+      </c>
+      <c r="C16" s="5">
         <v>1808</v>
       </c>
-      <c r="C16">
+      <c r="D16" s="5">
         <v>2061</v>
       </c>
-      <c r="D16">
+      <c r="E16" s="5">
         <v>2361</v>
       </c>
-      <c r="E16">
+      <c r="F16" s="5">
         <v>2720</v>
       </c>
-      <c r="F16">
+      <c r="G16" s="5">
         <v>2990</v>
       </c>
-      <c r="G16">
+      <c r="H16" s="5">
         <v>3877</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="5">
         <v>4470</v>
       </c>
-      <c r="I16">
+      <c r="J16" s="5">
         <v>4968</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="5">
         <v>5633</v>
       </c>
-      <c r="K16">
+      <c r="L16" s="5">
         <v>5837</v>
       </c>
-      <c r="L16">
+      <c r="M16" s="5">
         <v>6301</v>
       </c>
-      <c r="M16">
+      <c r="N16" s="5">
         <v>7121</v>
       </c>
-      <c r="N16">
+      <c r="O16" s="5">
         <v>8282</v>
       </c>
-      <c r="O16">
+      <c r="P16" s="5">
         <v>9427</v>
       </c>
-      <c r="P16">
+      <c r="Q16" s="5">
         <v>9590</v>
       </c>
-      <c r="Q16">
+      <c r="R16" s="5">
         <v>9665</v>
       </c>
-      <c r="R16">
+      <c r="S16" s="5">
         <v>10171</v>
       </c>
-      <c r="S16">
+      <c r="T16" s="5">
         <v>10400</v>
       </c>
-      <c r="T16">
+      <c r="U16" s="5">
         <v>11138</v>
       </c>
-      <c r="U16" t="s">
-        <v>78</v>
-      </c>
-      <c r="V16">
+      <c r="V16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="W16" s="5">
         <v>13363</v>
       </c>
-      <c r="W16">
+      <c r="X16" s="5">
         <v>13944</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="6">
+        <v>1273</v>
+      </c>
+      <c r="C17" s="5">
         <v>1496</v>
       </c>
-      <c r="C17">
+      <c r="D17" s="5">
         <v>1784</v>
       </c>
-      <c r="D17">
+      <c r="E17" s="5">
         <v>2108</v>
       </c>
-      <c r="E17">
+      <c r="F17" s="5">
         <v>2478</v>
       </c>
-      <c r="F17">
+      <c r="G17" s="5">
         <v>2795</v>
       </c>
-      <c r="G17">
+      <c r="H17" s="5">
         <v>3633</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="5">
         <v>4354</v>
       </c>
-      <c r="I17">
+      <c r="J17" s="5">
         <v>4752</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="5">
         <v>5374</v>
       </c>
-      <c r="K17">
+      <c r="L17" s="5">
         <v>5493</v>
       </c>
-      <c r="L17">
+      <c r="M17" s="5">
         <v>6137</v>
       </c>
-      <c r="M17">
+      <c r="N17" s="5">
         <v>6740</v>
       </c>
-      <c r="N17">
+      <c r="O17" s="5">
         <v>7579</v>
       </c>
-      <c r="O17">
+      <c r="P17" s="5">
         <v>8626</v>
       </c>
-      <c r="P17">
+      <c r="Q17" s="5">
         <v>9035</v>
       </c>
-      <c r="Q17">
+      <c r="R17" s="5">
         <v>9065</v>
       </c>
-      <c r="R17">
+      <c r="S17" s="5">
         <v>9815</v>
       </c>
-      <c r="S17">
+      <c r="T17" s="5">
         <v>10326</v>
       </c>
-      <c r="T17">
+      <c r="U17" s="5">
         <v>10999</v>
       </c>
-      <c r="U17">
+      <c r="V17" s="5">
         <v>11134</v>
       </c>
-      <c r="V17">
+      <c r="W17" s="5">
         <v>13641</v>
       </c>
-      <c r="W17">
+      <c r="X17" s="5">
         <v>14231</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="4"/>
+      <c r="C18" s="5">
         <v>1783</v>
       </c>
-      <c r="C18">
+      <c r="D18" s="5">
         <v>1958</v>
       </c>
-      <c r="D18">
+      <c r="E18" s="5">
         <v>2255</v>
       </c>
-      <c r="E18">
+      <c r="F18" s="5">
         <v>2633</v>
       </c>
-      <c r="F18">
+      <c r="G18" s="5">
         <v>2995</v>
       </c>
-      <c r="G18">
+      <c r="H18" s="5">
         <v>3997</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="5">
         <v>4701</v>
       </c>
-      <c r="I18">
+      <c r="J18" s="5">
         <v>5113</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="5">
         <v>5386</v>
       </c>
-      <c r="K18">
+      <c r="L18" s="5">
         <v>5518</v>
       </c>
-      <c r="L18">
+      <c r="M18" s="5">
         <v>6080</v>
       </c>
-      <c r="M18">
+      <c r="N18" s="5">
         <v>6500</v>
       </c>
-      <c r="N18">
+      <c r="O18" s="5">
         <v>7300</v>
       </c>
-      <c r="O18">
+      <c r="P18" s="5">
         <v>8315</v>
       </c>
-      <c r="P18">
+      <c r="Q18" s="5">
         <v>8903</v>
       </c>
-      <c r="Q18">
+      <c r="R18" s="5">
         <v>8994</v>
       </c>
-      <c r="R18">
+      <c r="S18" s="5">
         <v>9451</v>
       </c>
-      <c r="S18">
+      <c r="T18" s="5">
         <v>9780</v>
       </c>
-      <c r="T18">
+      <c r="U18" s="5">
         <v>10668</v>
       </c>
-      <c r="U18">
+      <c r="V18" s="5">
         <v>10742</v>
       </c>
-      <c r="V18">
+      <c r="W18" s="5">
         <v>13085</v>
       </c>
-      <c r="W18">
+      <c r="X18" s="5">
         <v>13800</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4">
+        <v>2385</v>
+      </c>
+      <c r="C19" s="5">
         <v>2918</v>
       </c>
-      <c r="C19">
+      <c r="D19" s="5">
         <v>3208</v>
       </c>
-      <c r="D19">
+      <c r="E19" s="5">
         <v>3703</v>
       </c>
-      <c r="E19">
+      <c r="F19" s="5">
         <v>4171</v>
       </c>
-      <c r="F19">
+      <c r="G19" s="5">
         <v>5121</v>
       </c>
-      <c r="G19">
+      <c r="H19" s="5">
         <v>5855</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="5">
         <v>6648</v>
       </c>
-      <c r="I19">
+      <c r="J19" s="5">
         <v>7406</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="5">
         <v>8656</v>
       </c>
-      <c r="K19">
+      <c r="L19" s="5">
         <v>9128</v>
       </c>
-      <c r="L19">
+      <c r="M19" s="5">
         <v>9747</v>
       </c>
-      <c r="M19">
+      <c r="N19" s="5">
         <v>10965</v>
       </c>
-      <c r="N19">
+      <c r="O19" s="5">
         <v>12542</v>
       </c>
-      <c r="O19">
+      <c r="P19" s="5">
         <v>14413</v>
       </c>
-      <c r="P19">
+      <c r="Q19" s="5">
         <v>15092</v>
       </c>
-      <c r="Q19">
+      <c r="R19" s="5">
         <v>15397</v>
       </c>
-      <c r="R19">
+      <c r="S19" s="5">
         <v>16087</v>
       </c>
-      <c r="S19">
+      <c r="T19" s="5">
         <v>16843</v>
       </c>
-      <c r="T19">
+      <c r="U19" s="5">
         <v>17740</v>
       </c>
-      <c r="U19">
+      <c r="V19" s="5">
         <v>18029</v>
       </c>
-      <c r="V19">
+      <c r="W19" s="5">
         <v>20585</v>
       </c>
-      <c r="W19">
+      <c r="X19" s="5">
         <v>21718</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="4"/>
+      <c r="C20" s="5">
         <v>2054</v>
       </c>
-      <c r="C20">
+      <c r="D20" s="5">
         <v>2425</v>
       </c>
-      <c r="D20">
+      <c r="E20" s="5">
         <v>2784</v>
       </c>
-      <c r="E20">
+      <c r="F20" s="5">
         <v>3216</v>
       </c>
-      <c r="F20">
+      <c r="G20" s="5">
         <v>3699</v>
       </c>
-      <c r="G20">
+      <c r="H20" s="5">
         <v>4625</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="5">
         <v>5381</v>
       </c>
-      <c r="I20">
+      <c r="J20" s="5">
         <v>5990</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="5">
         <v>6754</v>
       </c>
-      <c r="K20">
+      <c r="L20" s="5">
         <v>7228</v>
       </c>
-      <c r="L20">
+      <c r="M20" s="5">
         <v>7774</v>
       </c>
-      <c r="M20">
+      <c r="N20" s="5">
         <v>8531</v>
       </c>
-      <c r="N20">
+      <c r="O20" s="5">
         <v>9682</v>
       </c>
-      <c r="O20">
+      <c r="P20" s="5">
         <v>11569</v>
       </c>
-      <c r="P20">
+      <c r="Q20" s="5">
         <v>12007</v>
       </c>
-      <c r="Q20">
+      <c r="R20" s="5">
         <v>12203</v>
       </c>
-      <c r="R20">
+      <c r="S20" s="5">
         <v>12829</v>
       </c>
-      <c r="S20">
+      <c r="T20" s="5">
         <v>13307</v>
       </c>
-      <c r="T20">
+      <c r="U20" s="5">
         <v>14196</v>
       </c>
-      <c r="U20">
+      <c r="V20" s="5">
         <v>14467</v>
       </c>
-      <c r="V20">
+      <c r="W20" s="5">
         <v>16614</v>
       </c>
-      <c r="W20">
+      <c r="X20" s="5">
         <v>17877</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="6">
+        <v>1989</v>
+      </c>
+      <c r="C21" s="5">
         <v>2404</v>
       </c>
-      <c r="C21">
+      <c r="D21" s="5">
         <v>2823</v>
       </c>
-      <c r="D21">
+      <c r="E21" s="5">
         <v>3229</v>
       </c>
-      <c r="E21">
+      <c r="F21" s="5">
         <v>3750</v>
       </c>
-      <c r="F21">
+      <c r="G21" s="5">
         <v>4525</v>
       </c>
-      <c r="G21">
+      <c r="H21" s="5">
         <v>5167</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="5">
         <v>6198</v>
       </c>
-      <c r="I21">
+      <c r="J21" s="5">
         <v>6798</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="5">
         <v>7556</v>
       </c>
-      <c r="K21">
+      <c r="L21" s="5">
         <v>8226</v>
       </c>
-      <c r="L21">
+      <c r="M21" s="5">
         <v>8293</v>
       </c>
-      <c r="M21">
+      <c r="N21" s="5">
         <v>9496</v>
       </c>
-      <c r="N21">
+      <c r="O21" s="5">
         <v>10817</v>
       </c>
-      <c r="O21">
+      <c r="P21" s="5">
         <v>12069</v>
       </c>
-      <c r="P21">
+      <c r="Q21" s="5">
         <v>12128</v>
       </c>
-      <c r="Q21">
+      <c r="R21" s="5">
         <v>12539</v>
       </c>
-      <c r="R21">
+      <c r="S21" s="5">
         <v>12948</v>
       </c>
-      <c r="S21">
+      <c r="T21" s="5">
         <v>13791</v>
       </c>
-      <c r="T21">
+      <c r="U21" s="5">
         <v>14567</v>
       </c>
-      <c r="U21">
+      <c r="V21" s="5">
         <v>14567</v>
       </c>
-      <c r="V21">
+      <c r="W21" s="5">
         <v>16905</v>
       </c>
-      <c r="W21">
+      <c r="X21" s="5">
         <v>17463</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="6">
+        <v>1806</v>
+      </c>
+      <c r="C22" s="5">
         <v>2217</v>
       </c>
-      <c r="C22">
+      <c r="D22" s="5">
         <v>2505</v>
       </c>
-      <c r="D22">
+      <c r="E22" s="5">
         <v>2866</v>
       </c>
-      <c r="E22">
+      <c r="F22" s="5">
         <v>3574</v>
       </c>
-      <c r="F22">
+      <c r="G22" s="5">
         <v>4060</v>
       </c>
-      <c r="G22">
+      <c r="H22" s="5">
         <v>4907</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="5">
         <v>5661</v>
       </c>
-      <c r="I22">
+      <c r="J22" s="5">
         <v>6210</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="5">
         <v>7308</v>
       </c>
-      <c r="K22">
+      <c r="L22" s="5">
         <v>7722</v>
       </c>
-      <c r="L22">
+      <c r="M22" s="5">
         <v>8159</v>
       </c>
-      <c r="M22">
+      <c r="N22" s="5">
         <v>10243</v>
       </c>
-      <c r="N22">
+      <c r="O22" s="5">
         <v>11323</v>
       </c>
-      <c r="O22">
+      <c r="P22" s="5">
         <v>12880</v>
       </c>
-      <c r="P22">
+      <c r="Q22" s="5">
         <v>10944</v>
       </c>
-      <c r="Q22">
+      <c r="R22" s="5">
         <v>11380</v>
       </c>
-      <c r="R22">
+      <c r="S22" s="5">
         <v>11816</v>
       </c>
-      <c r="S22">
+      <c r="T22" s="5">
         <v>12334</v>
       </c>
-      <c r="T22">
+      <c r="U22" s="5">
         <v>13304</v>
       </c>
-      <c r="U22">
+      <c r="V22" s="5">
         <v>13857</v>
       </c>
-      <c r="V22">
+      <c r="W22" s="5">
         <v>16147</v>
       </c>
-      <c r="W22">
+      <c r="X22" s="5">
         <v>16675</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="4"/>
+      <c r="C23" s="5">
         <v>1859</v>
       </c>
-      <c r="C23">
+      <c r="D23" s="5">
         <v>2026</v>
       </c>
-      <c r="D23">
+      <c r="E23" s="5">
         <v>2354</v>
       </c>
-      <c r="E23">
+      <c r="F23" s="5">
         <v>3011</v>
       </c>
-      <c r="F23">
+      <c r="G23" s="5">
         <v>3450</v>
       </c>
-      <c r="G23">
+      <c r="H23" s="5">
         <v>4073</v>
       </c>
-      <c r="H23">
+      <c r="I23" s="5">
         <v>4851</v>
       </c>
-      <c r="I23">
+      <c r="J23" s="5">
         <v>5270</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="5">
         <v>6066</v>
       </c>
-      <c r="K23">
+      <c r="L23" s="5">
         <v>6346</v>
       </c>
-      <c r="L23">
+      <c r="M23" s="5">
         <v>6847</v>
       </c>
-      <c r="M23">
+      <c r="N23" s="5">
         <v>7474</v>
       </c>
-      <c r="N23">
+      <c r="O23" s="5">
         <v>8578</v>
       </c>
-      <c r="O23">
+      <c r="P23" s="5">
         <v>9678</v>
       </c>
-      <c r="P23">
+      <c r="Q23" s="5">
         <v>9980</v>
       </c>
-      <c r="Q23">
+      <c r="R23" s="5">
         <v>10234</v>
       </c>
-      <c r="R23">
+      <c r="S23" s="5">
         <v>10698</v>
       </c>
-      <c r="S23">
+      <c r="T23" s="5">
         <v>10691</v>
       </c>
-      <c r="T23">
+      <c r="U23" s="5">
         <v>11428</v>
       </c>
-      <c r="U23">
+      <c r="V23" s="5">
         <v>11767</v>
       </c>
-      <c r="V23">
+      <c r="W23" s="5">
         <v>14059</v>
       </c>
-      <c r="W23">
+      <c r="X23" s="5">
         <v>14519</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
+        <v>1774</v>
+      </c>
+      <c r="C24" s="5">
         <v>1930</v>
       </c>
-      <c r="C24">
+      <c r="D24" s="5">
         <v>2346</v>
       </c>
-      <c r="D24">
+      <c r="E24" s="5">
         <v>2703</v>
       </c>
-      <c r="E24">
+      <c r="F24" s="5">
         <v>3221</v>
       </c>
-      <c r="F24">
+      <c r="G24" s="5">
         <v>3696</v>
       </c>
-      <c r="G24">
+      <c r="H24" s="5">
         <v>4097</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="5">
         <v>4995</v>
       </c>
-      <c r="I24">
+      <c r="J24" s="5">
         <v>5209</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="5">
         <v>5729</v>
       </c>
-      <c r="K24">
+      <c r="L24" s="5">
         <v>5955</v>
       </c>
-      <c r="L24">
+      <c r="M24" s="5">
         <v>6273</v>
       </c>
-      <c r="M24">
+      <c r="N24" s="5">
         <v>7026</v>
       </c>
-      <c r="N24">
+      <c r="O24" s="5">
         <v>8021</v>
       </c>
-      <c r="O24">
+      <c r="P24" s="5">
         <v>9630</v>
       </c>
-      <c r="P24">
+      <c r="Q24" s="5">
         <v>9948</v>
       </c>
-      <c r="Q24">
+      <c r="R24" s="5">
         <v>10343</v>
       </c>
-      <c r="R24">
+      <c r="S24" s="5">
         <v>10939</v>
       </c>
-      <c r="S24">
+      <c r="T24" s="5">
         <v>11392</v>
       </c>
-      <c r="T24">
+      <c r="U24" s="5">
         <v>12084</v>
       </c>
-      <c r="U24">
+      <c r="V24" s="5">
         <v>12067</v>
       </c>
-      <c r="V24">
+      <c r="W24" s="5">
         <v>14337</v>
       </c>
-      <c r="W24">
+      <c r="X24" s="5">
         <v>14806</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="5">
         <v>1899</v>
       </c>
-      <c r="C25">
+      <c r="D25" s="5">
         <v>2185</v>
       </c>
-      <c r="D25">
+      <c r="E25" s="5">
         <v>2524</v>
       </c>
-      <c r="E25">
+      <c r="F25" s="5">
         <v>2829</v>
       </c>
-      <c r="F25">
+      <c r="G25" s="5">
         <v>3321</v>
       </c>
-      <c r="G25">
+      <c r="H25" s="5">
         <v>3835</v>
       </c>
-      <c r="H25">
+      <c r="I25" s="5">
         <v>4400</v>
       </c>
-      <c r="I25">
+      <c r="J25" s="5">
         <v>4843</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="5">
         <v>5380</v>
       </c>
-      <c r="K25">
+      <c r="L25" s="5">
         <v>5775</v>
       </c>
-      <c r="L25">
+      <c r="M25" s="5">
         <v>6155</v>
       </c>
-      <c r="M25">
+      <c r="N25" s="5">
         <v>6524</v>
       </c>
-      <c r="N25">
+      <c r="O25" s="5">
         <v>6984</v>
       </c>
-      <c r="O25">
+      <c r="P25" s="5">
         <v>8722</v>
       </c>
-      <c r="P25">
+      <c r="Q25" s="5">
         <v>9211</v>
       </c>
-      <c r="Q25">
+      <c r="R25" s="5">
         <v>9628</v>
       </c>
-      <c r="R25">
+      <c r="S25" s="5">
         <v>10239</v>
       </c>
-      <c r="S25">
+      <c r="T25" s="5">
         <v>11028</v>
       </c>
-      <c r="T25">
+      <c r="U25" s="5">
         <v>11289</v>
       </c>
-      <c r="U25">
+      <c r="V25" s="5">
         <v>11289</v>
       </c>
-      <c r="V25">
+      <c r="W25" s="5">
         <v>14059</v>
       </c>
-      <c r="W25">
+      <c r="X25" s="5">
         <v>14806</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="4">
+        <v>2359</v>
+      </c>
+      <c r="C26" s="5">
         <v>2996</v>
       </c>
-      <c r="C26">
+      <c r="D26" s="5">
         <v>3377</v>
       </c>
-      <c r="D26">
+      <c r="E26" s="5">
         <v>3798</v>
       </c>
-      <c r="E26">
+      <c r="F26" s="5">
         <v>4820</v>
       </c>
-      <c r="F26">
+      <c r="G26" s="5">
         <v>5333</v>
       </c>
-      <c r="G26">
+      <c r="H26" s="5">
         <v>5930</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="5">
         <v>6960</v>
       </c>
-      <c r="I26">
+      <c r="J26" s="5">
         <v>7579</v>
       </c>
-      <c r="J26">
+      <c r="K26" s="5">
         <v>8432</v>
       </c>
-      <c r="K26">
+      <c r="L26" s="5">
         <v>8737</v>
       </c>
-      <c r="L26">
+      <c r="M26" s="5">
         <v>9315</v>
       </c>
-      <c r="M26">
+      <c r="N26" s="5">
         <v>10113</v>
       </c>
-      <c r="N26">
+      <c r="O26" s="5">
         <v>11627</v>
       </c>
-      <c r="O26">
+      <c r="P26" s="5">
         <v>13582</v>
       </c>
-      <c r="P26">
+      <c r="Q26" s="5">
         <v>13562</v>
       </c>
-      <c r="Q26">
+      <c r="R26" s="5">
         <v>13787</v>
       </c>
-      <c r="R26">
+      <c r="S26" s="5">
         <v>14649</v>
       </c>
-      <c r="S26">
+      <c r="T26" s="5">
         <v>16688</v>
       </c>
-      <c r="T26">
+      <c r="U26" s="5">
         <v>17723</v>
       </c>
-      <c r="U26">
+      <c r="V26" s="5">
         <v>18625</v>
       </c>
-      <c r="V26">
+      <c r="W26" s="5">
         <v>22250</v>
       </c>
-      <c r="W26">
+      <c r="X26" s="5">
         <v>23474</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="4"/>
+      <c r="C27" s="5">
         <v>1791</v>
       </c>
-      <c r="C27">
+      <c r="D27" s="5">
         <v>2053</v>
       </c>
-      <c r="D27">
+      <c r="E27" s="5">
         <v>2401</v>
       </c>
-      <c r="E27">
+      <c r="F27" s="5">
         <v>2825</v>
       </c>
-      <c r="F27">
+      <c r="G27" s="5">
         <v>3225</v>
       </c>
-      <c r="G27">
+      <c r="H27" s="5">
         <v>3964</v>
       </c>
-      <c r="H27">
+      <c r="I27" s="5">
         <v>4617</v>
       </c>
-      <c r="I27">
+      <c r="J27" s="5">
         <v>4924</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="5">
         <v>5569</v>
       </c>
-      <c r="K27">
+      <c r="L27" s="5">
         <v>5801</v>
       </c>
-      <c r="L27">
+      <c r="M27" s="5">
         <v>6183</v>
       </c>
-      <c r="M27">
+      <c r="N27" s="5">
         <v>7166</v>
       </c>
-      <c r="N27">
+      <c r="O27" s="5">
         <v>7915</v>
       </c>
-      <c r="O27">
+      <c r="P27" s="5">
         <v>9221</v>
       </c>
-      <c r="P27">
+      <c r="Q27" s="5">
         <v>9751</v>
       </c>
-      <c r="Q27">
+      <c r="R27" s="5">
         <v>9886</v>
       </c>
-      <c r="R27">
+      <c r="S27" s="5">
         <v>10407</v>
       </c>
-      <c r="S27">
+      <c r="T27" s="5">
         <v>10673</v>
       </c>
-      <c r="T27">
+      <c r="U27" s="5">
         <v>11352</v>
       </c>
-      <c r="U27">
+      <c r="V27" s="5">
         <v>11408</v>
       </c>
-      <c r="V27">
+      <c r="W27" s="5">
         <v>13641</v>
       </c>
-      <c r="W27">
+      <c r="X27" s="5">
         <v>14088</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
+        <v>1345</v>
+      </c>
+      <c r="C28" s="5">
         <v>1571</v>
       </c>
-      <c r="C28">
+      <c r="D28" s="5">
         <v>1820</v>
       </c>
-      <c r="D28">
+      <c r="E28" s="5">
         <v>2060</v>
       </c>
-      <c r="E28">
+      <c r="F28" s="5">
         <v>2471</v>
       </c>
-      <c r="F28">
+      <c r="G28" s="5">
         <v>2951</v>
       </c>
-      <c r="G28">
+      <c r="H28" s="5">
         <v>3559</v>
       </c>
-      <c r="H28">
+      <c r="I28" s="5">
         <v>4247</v>
       </c>
-      <c r="I28">
+      <c r="J28" s="5">
         <v>4603</v>
       </c>
-      <c r="J28">
+      <c r="K28" s="5">
         <v>5254</v>
       </c>
-      <c r="K28">
+      <c r="L28" s="5">
         <v>6113</v>
       </c>
-      <c r="L28">
+      <c r="M28" s="5">
         <v>6406</v>
       </c>
-      <c r="M28">
+      <c r="N28" s="5">
         <v>7337</v>
       </c>
-      <c r="N28">
+      <c r="O28" s="5">
         <v>8518</v>
       </c>
-      <c r="O28">
+      <c r="P28" s="5">
         <v>10008</v>
       </c>
-      <c r="P28">
+      <c r="Q28" s="5">
         <v>10417</v>
       </c>
-      <c r="Q28">
+      <c r="R28" s="5">
         <v>10184</v>
       </c>
-      <c r="R28">
+      <c r="S28" s="5">
         <v>10623</v>
       </c>
-      <c r="S28">
+      <c r="T28" s="5">
         <v>10633</v>
       </c>
-      <c r="T28">
+      <c r="U28" s="5">
         <v>11441</v>
       </c>
-      <c r="U28">
+      <c r="V28" s="5">
         <v>11807</v>
       </c>
-      <c r="V28">
+      <c r="W28" s="5">
         <v>13780</v>
       </c>
-      <c r="W28">
+      <c r="X28" s="5">
         <v>14231</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="4"/>
+      <c r="C29" s="5">
         <v>2291</v>
       </c>
-      <c r="C29">
+      <c r="D29" s="5">
         <v>2601</v>
       </c>
-      <c r="D29">
+      <c r="E29" s="5">
         <v>2919</v>
       </c>
-      <c r="E29">
+      <c r="F29" s="5">
         <v>3259</v>
       </c>
-      <c r="F29">
+      <c r="G29" s="5">
         <v>3544</v>
       </c>
-      <c r="G29">
+      <c r="H29" s="5">
         <v>4158</v>
       </c>
-      <c r="H29">
+      <c r="I29" s="5">
         <v>4901</v>
       </c>
-      <c r="I29">
+      <c r="J29" s="5">
         <v>5232</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="5">
         <v>5773</v>
       </c>
-      <c r="K29">
+      <c r="L29" s="5">
         <v>6221</v>
       </c>
-      <c r="L29">
+      <c r="M29" s="5">
         <v>6613</v>
       </c>
-      <c r="M29">
+      <c r="N29" s="5">
         <v>7072</v>
       </c>
-      <c r="N29">
+      <c r="O29" s="5">
         <v>8479</v>
       </c>
-      <c r="O29">
+      <c r="P29" s="5">
         <v>10043</v>
       </c>
-      <c r="P29">
+      <c r="Q29" s="5">
         <v>10526</v>
       </c>
-      <c r="Q29">
+      <c r="R29" s="5">
         <v>10792</v>
       </c>
-      <c r="R29">
+      <c r="S29" s="5">
         <v>11055</v>
       </c>
-      <c r="S29">
+      <c r="T29" s="5">
         <v>11500</v>
       </c>
-      <c r="T29">
+      <c r="U29" s="5">
         <v>11910</v>
       </c>
-      <c r="U29" t="s">
-        <v>79</v>
-      </c>
-      <c r="V29">
+      <c r="V29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="W29" s="5">
         <v>14476</v>
       </c>
-      <c r="W29">
+      <c r="X29" s="5">
         <v>15094</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="4">
+        <v>1292</v>
+      </c>
+      <c r="C30" s="5">
         <v>1449</v>
       </c>
-      <c r="C30">
+      <c r="D30" s="5">
         <v>1665</v>
       </c>
-      <c r="D30">
+      <c r="E30" s="5">
         <v>2074</v>
       </c>
-      <c r="E30">
+      <c r="F30" s="5">
         <v>2540</v>
       </c>
-      <c r="F30">
+      <c r="G30" s="5">
         <v>2962</v>
       </c>
-      <c r="G30">
+      <c r="H30" s="5">
         <v>3531</v>
       </c>
-      <c r="H30">
+      <c r="I30" s="5">
         <v>4102</v>
       </c>
-      <c r="I30">
+      <c r="J30" s="5">
         <v>4393</v>
       </c>
-      <c r="J30">
+      <c r="K30" s="5">
         <v>4914</v>
       </c>
-      <c r="K30">
+      <c r="L30" s="5">
         <v>5100</v>
       </c>
-      <c r="L30">
+      <c r="M30" s="5">
         <v>5525</v>
       </c>
-      <c r="M30">
+      <c r="N30" s="5">
         <v>6282</v>
       </c>
-      <c r="N30">
+      <c r="O30" s="5">
         <v>7164</v>
       </c>
-      <c r="O30">
+      <c r="P30" s="5">
         <v>8211</v>
       </c>
-      <c r="P30">
+      <c r="Q30" s="5">
         <v>8521</v>
       </c>
-      <c r="Q30">
+      <c r="R30" s="5">
         <v>8579</v>
       </c>
-      <c r="R30">
+      <c r="S30" s="5">
         <v>9012</v>
       </c>
-      <c r="S30">
+      <c r="T30" s="5">
         <v>9119</v>
       </c>
-      <c r="T30">
+      <c r="U30" s="5">
         <v>9876</v>
       </c>
-      <c r="U30">
+      <c r="V30" s="5">
         <v>9779</v>
       </c>
-      <c r="V30">
+      <c r="W30" s="5">
         <v>11970</v>
       </c>
-      <c r="W30">
+      <c r="X30" s="5">
         <v>12363</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="4">
+        <v>1399</v>
+      </c>
+      <c r="C31" s="5">
         <v>1637</v>
       </c>
-      <c r="C31">
+      <c r="D31" s="5">
         <v>1756</v>
       </c>
-      <c r="D31">
+      <c r="E31" s="5">
         <v>2079</v>
       </c>
-      <c r="E31">
+      <c r="F31" s="5">
         <v>2340</v>
       </c>
-      <c r="F31">
+      <c r="G31" s="5">
         <v>2664</v>
       </c>
-      <c r="G31">
+      <c r="H31" s="5">
         <v>3317</v>
       </c>
-      <c r="H31">
+      <c r="I31" s="5">
         <v>3700</v>
       </c>
-      <c r="I31">
+      <c r="J31" s="5">
         <v>4311</v>
       </c>
-      <c r="J31">
+      <c r="K31" s="5">
         <v>4956</v>
       </c>
-      <c r="K31">
+      <c r="L31" s="5">
         <v>5331</v>
       </c>
-      <c r="L31">
+      <c r="M31" s="5">
         <v>5722</v>
       </c>
-      <c r="M31">
+      <c r="N31" s="5">
         <v>6823</v>
       </c>
-      <c r="N31">
+      <c r="O31" s="5">
         <v>7750</v>
       </c>
-      <c r="O31">
+      <c r="P31" s="5">
         <v>7934</v>
       </c>
-      <c r="P31">
+      <c r="Q31" s="5">
         <v>8372</v>
       </c>
-      <c r="Q31">
+      <c r="R31" s="5">
         <v>8551</v>
       </c>
-      <c r="R31">
+      <c r="S31" s="5">
         <v>9120</v>
       </c>
-      <c r="S31">
+      <c r="T31" s="5">
         <v>9700</v>
       </c>
-      <c r="T31">
+      <c r="U31" s="5">
         <v>10443</v>
       </c>
-      <c r="U31">
+      <c r="V31" s="5">
         <v>10631</v>
       </c>
-      <c r="V31">
+      <c r="W31" s="5">
         <v>12945</v>
       </c>
-      <c r="W31">
+      <c r="X31" s="5">
         <v>13656</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="4">
+        <v>1400</v>
+      </c>
+      <c r="C32" s="5">
         <v>1676</v>
       </c>
-      <c r="C32">
+      <c r="D32" s="5">
         <v>1910</v>
       </c>
-      <c r="D32">
+      <c r="E32" s="5">
         <v>2278</v>
       </c>
-      <c r="E32">
+      <c r="F32" s="5">
         <v>2739</v>
       </c>
-      <c r="F32">
+      <c r="G32" s="5">
         <v>3278</v>
       </c>
-      <c r="G32">
+      <c r="H32" s="5">
         <v>3832</v>
       </c>
-      <c r="H32">
+      <c r="I32" s="5">
         <v>4458</v>
       </c>
-      <c r="I32">
+      <c r="J32" s="5">
         <v>5253</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="5">
         <v>5737</v>
       </c>
-      <c r="K32">
+      <c r="L32" s="5">
         <v>5976</v>
       </c>
-      <c r="L32">
+      <c r="M32" s="5">
         <v>6332</v>
       </c>
-      <c r="M32">
+      <c r="N32" s="5">
         <v>7155</v>
       </c>
-      <c r="N32">
+      <c r="O32" s="5">
         <v>8027</v>
       </c>
-      <c r="O32">
+      <c r="P32" s="5">
         <v>9261</v>
       </c>
-      <c r="P32">
+      <c r="Q32" s="5">
         <v>9603</v>
       </c>
-      <c r="Q32">
+      <c r="R32" s="5">
         <v>9925</v>
       </c>
-      <c r="R32">
+      <c r="S32" s="5">
         <v>10228</v>
       </c>
-      <c r="S32">
+      <c r="T32" s="5">
         <v>10621</v>
       </c>
-      <c r="T32">
+      <c r="U32" s="5">
         <v>11261</v>
       </c>
-      <c r="U32">
+      <c r="V32" s="5">
         <v>11397</v>
       </c>
-      <c r="V32">
+      <c r="W32" s="5">
         <v>13363</v>
       </c>
-      <c r="W32">
+      <c r="X32" s="5">
         <v>13800</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="4">
+        <v>1585</v>
+      </c>
+      <c r="C33" s="5">
         <v>1746</v>
       </c>
-      <c r="C33">
+      <c r="D33" s="5">
         <v>1949</v>
       </c>
-      <c r="D33">
+      <c r="E33" s="5">
         <v>2147</v>
       </c>
-      <c r="E33">
+      <c r="F33" s="5">
         <v>2528</v>
       </c>
-      <c r="F33">
+      <c r="G33" s="5">
         <v>2883</v>
       </c>
-      <c r="G33">
+      <c r="H33" s="5">
         <v>3466</v>
       </c>
-      <c r="H33">
+      <c r="I33" s="5">
         <v>4221</v>
       </c>
-      <c r="I33">
+      <c r="J33" s="5">
         <v>4598</v>
       </c>
-      <c r="J33">
+      <c r="K33" s="5">
         <v>5209</v>
       </c>
-      <c r="K33">
+      <c r="L33" s="5">
         <v>5378</v>
       </c>
-      <c r="L33">
+      <c r="M33" s="5">
         <v>5822</v>
       </c>
-      <c r="M33">
+      <c r="N33" s="5">
         <v>6271</v>
       </c>
-      <c r="N33">
+      <c r="O33" s="5">
         <v>7120</v>
       </c>
-      <c r="O33">
+      <c r="P33" s="5">
         <v>8236</v>
       </c>
-      <c r="P33">
+      <c r="Q33" s="5">
         <v>8730</v>
       </c>
-      <c r="Q33">
+      <c r="R33" s="5">
         <v>9040</v>
       </c>
-      <c r="R33">
+      <c r="S33" s="5">
         <v>9581</v>
       </c>
-      <c r="S33">
+      <c r="T33" s="5">
         <v>10114</v>
       </c>
-      <c r="T33">
+      <c r="U33" s="5">
         <v>10793</v>
       </c>
-      <c r="U33">
+      <c r="V33" s="5">
         <v>11069</v>
       </c>
-      <c r="V33">
+      <c r="W33" s="5">
         <v>13501</v>
       </c>
-      <c r="W33">
+      <c r="X33" s="5">
         <v>13944</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="4"/>
+      <c r="C34" s="5">
         <v>1693</v>
       </c>
-      <c r="C34">
+      <c r="D34" s="5">
         <v>1821</v>
       </c>
-      <c r="D34">
+      <c r="E34" s="5">
         <v>1978</v>
       </c>
-      <c r="E34">
+      <c r="F34" s="5">
         <v>2460</v>
       </c>
-      <c r="F34">
+      <c r="G34" s="5">
         <v>2762</v>
       </c>
-      <c r="G34">
+      <c r="H34" s="5">
         <v>3701</v>
       </c>
-      <c r="H34">
+      <c r="I34" s="5">
         <v>4301</v>
       </c>
-      <c r="I34">
+      <c r="J34" s="5">
         <v>4647</v>
       </c>
-      <c r="J34">
+      <c r="K34" s="5">
         <v>5583</v>
       </c>
-      <c r="K34">
+      <c r="L34" s="5">
         <v>5742</v>
       </c>
-      <c r="L34">
+      <c r="M34" s="5">
         <v>6474</v>
       </c>
-      <c r="M34">
+      <c r="N34" s="5">
         <v>6676</v>
       </c>
-      <c r="N34">
+      <c r="O34" s="5">
         <v>7901</v>
       </c>
-      <c r="O34">
+      <c r="P34" s="5">
         <v>8669</v>
       </c>
-      <c r="P34">
+      <c r="Q34" s="5">
         <v>8794</v>
       </c>
-      <c r="Q34">
+      <c r="R34" s="5">
         <v>8720</v>
       </c>
-      <c r="R34">
+      <c r="S34" s="5">
         <v>9174</v>
       </c>
-      <c r="S34">
+      <c r="T34" s="5">
         <v>9322</v>
       </c>
-      <c r="T34">
+      <c r="U34" s="5">
         <v>9864</v>
       </c>
-      <c r="U34">
+      <c r="V34" s="5">
         <v>10158</v>
       </c>
-      <c r="V34">
+      <c r="W34" s="5">
         <v>11970</v>
       </c>
-      <c r="W34">
+      <c r="X34" s="5">
         <v>12363</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="4">
+        <v>1384</v>
+      </c>
+      <c r="C35" s="5">
         <v>1715</v>
       </c>
-      <c r="C35">
+      <c r="D35" s="5">
         <v>1961</v>
       </c>
-      <c r="D35">
+      <c r="E35" s="5">
         <v>2180</v>
       </c>
-      <c r="E35">
+      <c r="F35" s="5">
         <v>2648</v>
       </c>
-      <c r="F35">
+      <c r="G35" s="5">
         <v>3086</v>
       </c>
-      <c r="G35">
+      <c r="H35" s="5">
         <v>3728</v>
       </c>
-      <c r="H35">
+      <c r="I35" s="5">
         <v>4339</v>
       </c>
-      <c r="I35">
+      <c r="J35" s="5">
         <v>4744</v>
       </c>
-      <c r="J35">
+      <c r="K35" s="5">
         <v>5442</v>
       </c>
-      <c r="K35">
+      <c r="L35" s="5">
         <v>5824</v>
       </c>
-      <c r="L35">
+      <c r="M35" s="5">
         <v>6233</v>
       </c>
-      <c r="M35">
+      <c r="N35" s="5">
         <v>6988</v>
       </c>
-      <c r="N35">
+      <c r="O35" s="5">
         <v>7967</v>
       </c>
-      <c r="O35">
+      <c r="P35" s="5">
         <v>9109</v>
       </c>
-      <c r="P35">
+      <c r="Q35" s="5">
         <v>9414</v>
       </c>
-      <c r="Q35">
+      <c r="R35" s="5">
         <v>9262</v>
       </c>
-      <c r="R35">
+      <c r="S35" s="5">
         <v>9657</v>
       </c>
-      <c r="S35">
+      <c r="T35" s="5">
         <v>10039</v>
       </c>
-      <c r="T35">
+      <c r="U35" s="5">
         <v>10787</v>
       </c>
-      <c r="U35">
+      <c r="V35" s="5">
         <v>11053</v>
       </c>
-      <c r="V35">
+      <c r="W35" s="5">
         <v>13085</v>
       </c>
-      <c r="W35">
+      <c r="X35" s="5">
         <v>13513</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="6">
+        <v>1333</v>
+      </c>
+      <c r="C36" s="5">
         <v>1505</v>
       </c>
-      <c r="C36">
+      <c r="D36" s="5">
         <v>1694</v>
       </c>
-      <c r="D36">
+      <c r="E36" s="5">
         <v>1897</v>
       </c>
-      <c r="E36">
+      <c r="F36" s="5">
         <v>2227</v>
       </c>
-      <c r="F36">
+      <c r="G36" s="5">
         <v>2484</v>
       </c>
-      <c r="G36">
+      <c r="H36" s="5">
         <v>3153</v>
       </c>
-      <c r="H36">
+      <c r="I36" s="5">
         <v>3648</v>
       </c>
-      <c r="I36">
+      <c r="J36" s="5">
         <v>4066</v>
       </c>
-      <c r="J36">
+      <c r="K36" s="5">
         <v>4629</v>
       </c>
-      <c r="K36">
+      <c r="L36" s="5">
         <v>4871</v>
       </c>
-      <c r="L36">
+      <c r="M36" s="5">
         <v>5279</v>
       </c>
-      <c r="M36">
+      <c r="N36" s="5">
         <v>6791</v>
       </c>
-      <c r="N36">
+      <c r="O36" s="5">
         <v>7453</v>
       </c>
-      <c r="O36">
+      <c r="P36" s="5">
         <v>8658</v>
       </c>
-      <c r="P36">
+      <c r="Q36" s="5">
         <v>9076</v>
       </c>
-      <c r="Q36">
+      <c r="R36" s="5">
         <v>9239</v>
       </c>
-      <c r="R36">
+      <c r="S36" s="5">
         <v>9315</v>
       </c>
-      <c r="S36">
+      <c r="T36" s="5">
         <v>9766</v>
       </c>
-      <c r="T36">
+      <c r="U36" s="5">
         <v>10465</v>
       </c>
-      <c r="U36">
+      <c r="V36" s="5">
         <v>10628</v>
       </c>
-      <c r="V36">
+      <c r="W36" s="5">
         <v>12667</v>
       </c>
-      <c r="W36">
+      <c r="X36" s="5">
         <v>13081</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>31</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="6">
+        <v>1753</v>
+      </c>
+      <c r="C37" s="5">
         <v>1897</v>
       </c>
-      <c r="C37">
+      <c r="D37" s="5">
         <v>2026</v>
       </c>
-      <c r="D37">
+      <c r="E37" s="5">
         <v>2193</v>
       </c>
-      <c r="E37">
+      <c r="F37" s="5">
         <v>2568</v>
       </c>
-      <c r="F37">
+      <c r="G37" s="5">
         <v>2839</v>
       </c>
-      <c r="G37">
+      <c r="H37" s="5">
         <v>3172</v>
       </c>
-      <c r="H37">
+      <c r="I37" s="5">
         <v>3986</v>
       </c>
-      <c r="I37">
+      <c r="J37" s="5">
         <v>4439</v>
       </c>
-      <c r="J37">
+      <c r="K37" s="5">
         <v>4800</v>
       </c>
-      <c r="K37">
+      <c r="L37" s="5">
         <v>4959</v>
       </c>
-      <c r="L37">
+      <c r="M37" s="5">
         <v>5081</v>
       </c>
-      <c r="M37">
+      <c r="N37" s="5">
         <v>6803</v>
       </c>
-      <c r="N37">
+      <c r="O37" s="5">
         <v>7396</v>
       </c>
-      <c r="O37">
+      <c r="P37" s="5">
         <v>8567</v>
       </c>
-      <c r="P37">
+      <c r="Q37" s="5">
         <v>8881</v>
       </c>
-      <c r="Q37">
+      <c r="R37" s="5">
         <v>9111</v>
       </c>
-      <c r="R37">
+      <c r="S37" s="5">
         <v>9992</v>
       </c>
-      <c r="S37">
+      <c r="T37" s="5">
         <v>10012</v>
       </c>
-      <c r="T37">
+      <c r="U37" s="5">
         <v>10353</v>
       </c>
-      <c r="U37">
+      <c r="V37" s="5">
         <v>10964</v>
       </c>
-      <c r="V37">
+      <c r="W37" s="5">
         <v>13085</v>
       </c>
-      <c r="W37">
+      <c r="X37" s="5">
         <v>13513</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>32</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="4"/>
+      <c r="C38" s="5">
         <v>1517</v>
       </c>
-      <c r="C38">
+      <c r="D38" s="5">
         <v>1624</v>
       </c>
-      <c r="D38">
+      <c r="E38" s="5">
         <v>1823</v>
       </c>
-      <c r="E38">
+      <c r="F38" s="5">
         <v>2231</v>
       </c>
-      <c r="F38">
+      <c r="G38" s="5">
         <v>2558</v>
       </c>
-      <c r="G38">
+      <c r="H38" s="5">
         <v>3034</v>
       </c>
-      <c r="H38">
+      <c r="I38" s="5">
         <v>3538</v>
       </c>
-      <c r="I38">
+      <c r="J38" s="5">
         <v>3847</v>
       </c>
-      <c r="J38">
+      <c r="K38" s="5">
         <v>4726</v>
       </c>
-      <c r="K38">
+      <c r="L38" s="5">
         <v>4918</v>
       </c>
-      <c r="L38">
+      <c r="M38" s="5">
         <v>5138</v>
       </c>
-      <c r="M38">
+      <c r="N38" s="5">
         <v>6573</v>
       </c>
-      <c r="N38">
+      <c r="O38" s="5">
         <v>7357</v>
       </c>
-      <c r="O38">
+      <c r="P38" s="5">
         <v>9366</v>
       </c>
-      <c r="P38">
+      <c r="Q38" s="5">
         <v>10183</v>
       </c>
-      <c r="Q38">
+      <c r="R38" s="5">
         <v>10140</v>
       </c>
-      <c r="R38">
+      <c r="S38" s="5">
         <v>10497</v>
       </c>
-      <c r="S38">
+      <c r="T38" s="5">
         <v>10872</v>
       </c>
-      <c r="T38">
+      <c r="U38" s="5">
         <v>11311</v>
       </c>
-      <c r="U38">
+      <c r="V38" s="5">
         <v>12576</v>
       </c>
-      <c r="V38">
+      <c r="W38" s="5">
         <v>14894</v>
       </c>
-      <c r="W38">
+      <c r="X38" s="5">
         <v>15381</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>34</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="6">
+        <v>1212</v>
+      </c>
+      <c r="C39" s="5">
         <v>1508</v>
       </c>
-      <c r="C39">
+      <c r="D39" s="5">
         <v>1740</v>
       </c>
-      <c r="D39">
+      <c r="E39" s="5">
         <v>1973</v>
       </c>
-      <c r="E39">
+      <c r="F39" s="5">
         <v>2347</v>
       </c>
-      <c r="F39">
+      <c r="G39" s="5">
         <v>2709</v>
       </c>
-      <c r="G39">
+      <c r="H39" s="5">
         <v>3144</v>
       </c>
-      <c r="H39">
+      <c r="I39" s="5">
         <v>3640</v>
       </c>
-      <c r="I39">
+      <c r="J39" s="5">
         <v>4119</v>
       </c>
-      <c r="J39">
+      <c r="K39" s="5">
         <v>4894</v>
       </c>
-      <c r="K39">
+      <c r="L39" s="5">
         <v>5081</v>
       </c>
-      <c r="L39">
+      <c r="M39" s="5">
         <v>5435</v>
       </c>
-      <c r="M39">
+      <c r="N39" s="5">
         <v>6625</v>
       </c>
-      <c r="N39">
+      <c r="O39" s="5">
         <v>7339</v>
       </c>
-      <c r="O39">
+      <c r="P39" s="5">
         <v>8530</v>
       </c>
-      <c r="P39">
+      <c r="Q39" s="5">
         <v>8815</v>
       </c>
-      <c r="Q39">
+      <c r="R39" s="5">
         <v>8719</v>
       </c>
-      <c r="R39">
+      <c r="S39" s="5">
         <v>9251</v>
       </c>
-      <c r="S39">
+      <c r="T39" s="5">
         <v>9655</v>
       </c>
-      <c r="T39">
+      <c r="U39" s="5">
         <v>10277</v>
       </c>
-      <c r="U39">
+      <c r="V39" s="5">
         <v>10451</v>
       </c>
-      <c r="V39">
+      <c r="W39" s="5">
         <v>12627</v>
       </c>
-      <c r="W39">
+      <c r="X39" s="5">
         <v>13225</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
-      </c>
-      <c r="B40">
+        <v>75</v>
+      </c>
+      <c r="B40" s="6">
+        <v>1237</v>
+      </c>
+      <c r="C40" s="5">
         <v>1445</v>
       </c>
-      <c r="C40">
+      <c r="D40" s="5">
         <v>1535</v>
       </c>
-      <c r="D40">
+      <c r="E40" s="5">
         <v>1841</v>
       </c>
-      <c r="E40">
+      <c r="F40" s="5">
         <v>2091</v>
       </c>
-      <c r="F40">
+      <c r="G40" s="5">
         <v>2638</v>
       </c>
-      <c r="G40">
+      <c r="H40" s="5">
         <v>3029</v>
       </c>
-      <c r="H40">
+      <c r="I40" s="5">
         <v>3570</v>
       </c>
-      <c r="I40">
+      <c r="J40" s="5">
         <v>3895</v>
       </c>
-      <c r="J40">
+      <c r="K40" s="5">
         <v>4776</v>
       </c>
-      <c r="K40">
+      <c r="L40" s="5">
         <v>4984</v>
       </c>
-      <c r="L40">
+      <c r="M40" s="5">
         <v>5468</v>
       </c>
-      <c r="M40">
+      <c r="N40" s="5">
         <v>6496</v>
       </c>
-      <c r="N40">
+      <c r="O40" s="5">
         <v>7284</v>
       </c>
-      <c r="O40">
+      <c r="P40" s="5">
         <v>8578</v>
       </c>
-      <c r="P40">
+      <c r="Q40" s="5">
         <v>8896</v>
       </c>
-      <c r="Q40">
+      <c r="R40" s="5">
         <v>8742</v>
       </c>
-      <c r="R40">
+      <c r="S40" s="5">
         <v>9014</v>
       </c>
-      <c r="S40">
+      <c r="T40" s="5">
         <v>9231</v>
       </c>
-      <c r="T40">
+      <c r="U40" s="5">
         <v>9854</v>
       </c>
-      <c r="U40">
+      <c r="V40" s="5">
         <v>10596</v>
       </c>
-      <c r="V40">
+      <c r="W40" s="5">
         <v>12528</v>
       </c>
-      <c r="W40">
+      <c r="X40" s="5">
         <v>12938</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>36</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="6">
+        <v>1389</v>
+      </c>
+      <c r="C41" s="5">
         <v>1680</v>
       </c>
-      <c r="C41">
+      <c r="D41" s="5">
         <v>1962</v>
       </c>
-      <c r="D41">
+      <c r="E41" s="5">
         <v>2244</v>
       </c>
-      <c r="E41">
+      <c r="F41" s="5">
         <v>2594</v>
       </c>
-      <c r="F41">
+      <c r="G41" s="5">
         <v>3050</v>
       </c>
-      <c r="G41">
+      <c r="H41" s="5">
         <v>3523</v>
       </c>
-      <c r="H41">
+      <c r="I41" s="5">
         <v>4331</v>
       </c>
-      <c r="I41">
+      <c r="J41" s="5">
         <v>4820</v>
       </c>
-      <c r="J41">
+      <c r="K41" s="5">
         <v>5539</v>
       </c>
-      <c r="K41">
+      <c r="L41" s="5">
         <v>5802</v>
       </c>
-      <c r="L41">
+      <c r="M41" s="5">
         <v>6259</v>
       </c>
-      <c r="M41">
+      <c r="N41" s="5">
         <v>6543</v>
       </c>
-      <c r="N41">
+      <c r="O41" s="5">
         <v>7154</v>
       </c>
-      <c r="O41">
+      <c r="P41" s="5">
         <v>8027</v>
       </c>
-      <c r="P41">
+      <c r="Q41" s="5">
         <v>8148</v>
       </c>
-      <c r="Q41">
+      <c r="R41" s="5">
         <v>8248</v>
       </c>
-      <c r="R41">
+      <c r="S41" s="5">
         <v>8622</v>
       </c>
-      <c r="S41">
+      <c r="T41" s="5">
         <v>8973</v>
       </c>
-      <c r="T41">
+      <c r="U41" s="5">
         <v>9777</v>
       </c>
-      <c r="U41">
+      <c r="V41" s="5">
         <v>10081</v>
       </c>
-      <c r="W41">
+      <c r="W41" s="5"/>
+      <c r="X41" s="5">
         <v>12938</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="6">
+        <v>1353</v>
+      </c>
+      <c r="C42" s="5">
         <v>1574</v>
       </c>
-      <c r="C42">
+      <c r="D42" s="5">
         <v>1780</v>
       </c>
-      <c r="D42">
+      <c r="E42" s="5">
         <v>2001</v>
       </c>
-      <c r="E42">
+      <c r="F42" s="5">
         <v>2390</v>
       </c>
-      <c r="F42">
+      <c r="G42" s="5">
         <v>2973</v>
       </c>
-      <c r="G42">
+      <c r="H42" s="5">
         <v>3371</v>
       </c>
-      <c r="H42">
+      <c r="I42" s="5">
         <v>3974</v>
       </c>
-      <c r="I42">
+      <c r="J42" s="5">
         <v>4274</v>
       </c>
-      <c r="J42">
+      <c r="K42" s="5">
         <v>5255</v>
       </c>
-      <c r="K42">
+      <c r="L42" s="5">
         <v>5407</v>
       </c>
-      <c r="L42">
+      <c r="M42" s="5">
         <v>5755</v>
       </c>
-      <c r="M42">
+      <c r="N42" s="5">
         <v>6446</v>
       </c>
-      <c r="N42">
+      <c r="O42" s="5">
         <v>7234</v>
       </c>
-      <c r="O42">
+      <c r="P42" s="5">
         <v>8428</v>
       </c>
-      <c r="P42">
+      <c r="Q42" s="5">
         <v>8323</v>
       </c>
-      <c r="Q42">
+      <c r="R42" s="5">
         <v>8318</v>
       </c>
-      <c r="R42">
+      <c r="S42" s="5">
         <v>8784</v>
       </c>
-      <c r="S42">
+      <c r="T42" s="5">
         <v>9222</v>
       </c>
-      <c r="T42">
+      <c r="U42" s="5">
         <v>9834</v>
       </c>
-      <c r="U42">
+      <c r="V42" s="5">
         <v>10015</v>
       </c>
-      <c r="V42">
+      <c r="W42" s="5">
         <v>12110</v>
       </c>
-      <c r="W42">
+      <c r="X42" s="5">
         <v>12650</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>41</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="6">
+        <v>1324</v>
+      </c>
+      <c r="C43" s="5">
         <v>1562</v>
       </c>
-      <c r="C43">
+      <c r="D43" s="5">
         <v>1748</v>
       </c>
-      <c r="D43">
+      <c r="E43" s="5">
         <v>2001</v>
       </c>
-      <c r="E43">
+      <c r="F43" s="5">
         <v>2305</v>
       </c>
-      <c r="F43">
+      <c r="G43" s="5">
         <v>2789</v>
       </c>
-      <c r="G43">
+      <c r="H43" s="5">
         <v>3277</v>
       </c>
-      <c r="H43">
+      <c r="I43" s="5">
         <v>3933</v>
       </c>
-      <c r="I43">
+      <c r="J43" s="5">
         <v>4292</v>
       </c>
-      <c r="J43">
+      <c r="K43" s="5">
         <v>5098</v>
       </c>
-      <c r="K43">
+      <c r="L43" s="5">
         <v>5114</v>
       </c>
-      <c r="L43">
+      <c r="M43" s="5">
         <v>5427</v>
       </c>
-      <c r="M43">
+      <c r="N43" s="5">
         <v>6198</v>
       </c>
-      <c r="N43">
+      <c r="O43" s="5">
         <v>7201</v>
       </c>
-      <c r="O43">
+      <c r="P43" s="5">
         <v>7863</v>
       </c>
-      <c r="P43">
+      <c r="Q43" s="5">
         <v>8682</v>
       </c>
-      <c r="Q43">
+      <c r="R43" s="5">
         <v>8742</v>
       </c>
-      <c r="R43">
+      <c r="S43" s="5">
         <v>8849</v>
       </c>
-      <c r="S43">
+      <c r="T43" s="5">
         <v>9258</v>
       </c>
-      <c r="T43">
+      <c r="U43" s="5">
         <v>9846</v>
       </c>
-      <c r="U43">
+      <c r="V43" s="5">
         <v>10184</v>
       </c>
-      <c r="V43">
+      <c r="W43" s="5">
         <v>12250</v>
       </c>
-      <c r="W43">
+      <c r="X43" s="5">
         <v>12650</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="6">
+        <v>1343</v>
+      </c>
+      <c r="C44" s="5">
         <v>1680</v>
       </c>
-      <c r="C44">
+      <c r="D44" s="5">
         <v>1821</v>
       </c>
-      <c r="D44">
+      <c r="E44" s="5">
         <v>2190</v>
       </c>
-      <c r="E44">
+      <c r="F44" s="5">
         <v>2454</v>
       </c>
-      <c r="F44">
+      <c r="G44" s="5">
         <v>2816</v>
       </c>
-      <c r="G44">
+      <c r="H44" s="5">
         <v>3260</v>
       </c>
-      <c r="H44">
+      <c r="I44" s="5">
         <v>3867</v>
       </c>
-      <c r="I44">
+      <c r="J44" s="5">
         <v>4228</v>
       </c>
-      <c r="J44">
+      <c r="K44" s="5">
         <v>5007</v>
       </c>
-      <c r="K44">
+      <c r="L44" s="5">
         <v>5352</v>
       </c>
-      <c r="L44">
+      <c r="M44" s="5">
         <v>5610</v>
       </c>
-      <c r="M44">
+      <c r="N44" s="5">
         <v>6260</v>
       </c>
-      <c r="N44">
+      <c r="O44" s="5">
         <v>6997</v>
       </c>
-      <c r="O44">
+      <c r="P44" s="5">
         <v>7775</v>
       </c>
-      <c r="P44">
+      <c r="Q44" s="5">
         <v>7776</v>
       </c>
-      <c r="Q44">
+      <c r="R44" s="5">
         <v>7824</v>
       </c>
-      <c r="R44">
+      <c r="S44" s="5">
         <v>8503</v>
       </c>
-      <c r="S44">
+      <c r="T44" s="5">
         <v>9181</v>
       </c>
-      <c r="T44">
+      <c r="U44" s="5">
         <v>9378</v>
       </c>
-      <c r="U44">
+      <c r="V44" s="5">
         <v>9716</v>
       </c>
-      <c r="V44">
+      <c r="W44" s="5">
         <v>11832</v>
       </c>
-      <c r="W44">
+      <c r="X44" s="5">
         <v>12219</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="4"/>
+      <c r="C45" s="5">
         <v>1599</v>
       </c>
-      <c r="C45">
+      <c r="D45" s="5">
         <v>1764</v>
       </c>
-      <c r="D45">
+      <c r="E45" s="5">
         <v>2012</v>
       </c>
-      <c r="E45">
+      <c r="F45" s="5">
         <v>2460</v>
       </c>
-      <c r="F45">
+      <c r="G45" s="5">
         <v>2695</v>
       </c>
-      <c r="G45">
+      <c r="H45" s="5">
         <v>3172</v>
       </c>
-      <c r="H45">
+      <c r="I45" s="5">
         <v>3846</v>
       </c>
-      <c r="I45">
+      <c r="J45" s="5">
         <v>4101</v>
       </c>
-      <c r="J45">
+      <c r="K45" s="5">
         <v>4733</v>
       </c>
-      <c r="K45">
+      <c r="L45" s="5">
         <v>5001</v>
       </c>
-      <c r="L45">
+      <c r="M45" s="5">
         <v>5622</v>
       </c>
-      <c r="M45">
+      <c r="N45" s="5">
         <v>6278</v>
       </c>
-      <c r="N45">
+      <c r="O45" s="5">
         <v>6988</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5">
         <v>8108</v>
       </c>
-      <c r="Q45">
+      <c r="R45" s="5">
         <v>8334</v>
       </c>
-      <c r="R45">
+      <c r="S45" s="5">
         <v>8709</v>
       </c>
-      <c r="S45">
+      <c r="T45" s="5">
         <v>8938</v>
       </c>
-      <c r="T45">
+      <c r="U45" s="5">
         <v>9600</v>
       </c>
-      <c r="U45">
+      <c r="V45" s="5">
         <v>9955</v>
       </c>
-      <c r="V45">
+      <c r="W45" s="5">
         <v>11832</v>
       </c>
-      <c r="W45">
+      <c r="X45" s="5">
         <v>12219</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="6">
+        <v>1383</v>
+      </c>
+      <c r="C46" s="5">
         <v>1687</v>
       </c>
-      <c r="C46">
+      <c r="D46" s="5">
         <v>1979</v>
       </c>
-      <c r="D46">
+      <c r="E46" s="5">
         <v>2178</v>
       </c>
-      <c r="E46">
+      <c r="F46" s="5">
         <v>2463</v>
       </c>
-      <c r="F46">
+      <c r="G46" s="5">
         <v>2947</v>
       </c>
-      <c r="G46">
+      <c r="H46" s="5">
         <v>3605</v>
       </c>
-      <c r="H46">
+      <c r="I46" s="5">
         <v>4065</v>
       </c>
-      <c r="I46">
+      <c r="J46" s="5">
         <v>4342</v>
       </c>
-      <c r="J46">
+      <c r="K46" s="5">
         <v>5090</v>
       </c>
-      <c r="K46">
+      <c r="L46" s="5">
         <v>5277</v>
       </c>
-      <c r="L46">
+      <c r="M46" s="5">
         <v>5753</v>
       </c>
-      <c r="M46">
+      <c r="N46" s="5">
         <v>6375</v>
       </c>
-      <c r="N46">
+      <c r="O46" s="5">
         <v>7324</v>
       </c>
-      <c r="O46">
+      <c r="P46" s="5">
         <v>8473</v>
       </c>
-      <c r="P46">
+      <c r="Q46" s="5">
         <v>8594</v>
       </c>
-      <c r="Q46">
+      <c r="R46" s="5">
         <v>8453</v>
       </c>
-      <c r="R46">
+      <c r="S46" s="5">
         <v>8975</v>
       </c>
-      <c r="S46">
+      <c r="T46" s="5">
         <v>9455</v>
       </c>
-      <c r="T46">
+      <c r="U46" s="5">
         <v>10314</v>
       </c>
-      <c r="U46">
+      <c r="V46" s="5">
         <v>10465</v>
       </c>
-      <c r="V46">
+      <c r="W46" s="5">
         <v>12388</v>
       </c>
-      <c r="W46">
+      <c r="X46" s="5">
         <v>12794</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>45</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="6">
+        <v>1294</v>
+      </c>
+      <c r="C47" s="5">
         <v>1621</v>
       </c>
-      <c r="C47">
+      <c r="D47" s="5">
         <v>1764</v>
       </c>
-      <c r="D47">
+      <c r="E47" s="5">
         <v>2007</v>
       </c>
-      <c r="E47">
+      <c r="F47" s="5">
         <v>2236</v>
       </c>
-      <c r="F47">
+      <c r="G47" s="5">
         <v>2712</v>
       </c>
-      <c r="G47">
+      <c r="H47" s="5">
         <v>3351</v>
       </c>
-      <c r="H47">
+      <c r="I47" s="5">
         <v>3981</v>
       </c>
-      <c r="I47">
+      <c r="J47" s="5">
         <v>4215</v>
       </c>
-      <c r="J47">
+      <c r="K47" s="5">
         <v>5007</v>
       </c>
-      <c r="K47">
+      <c r="L47" s="5">
         <v>5247</v>
       </c>
-      <c r="L47">
+      <c r="M47" s="5">
         <v>5510</v>
       </c>
-      <c r="M47">
+      <c r="N47" s="5">
         <v>6049</v>
       </c>
-      <c r="N47">
+      <c r="O47" s="5">
         <v>6988</v>
       </c>
-      <c r="O47">
+      <c r="P47" s="5">
         <v>8071</v>
       </c>
-      <c r="P47">
+      <c r="Q47" s="5">
         <v>8346</v>
       </c>
-      <c r="Q47">
+      <c r="R47" s="5">
         <v>8236</v>
       </c>
-      <c r="R47">
+      <c r="S47" s="5">
         <v>8657</v>
       </c>
-      <c r="S47">
+      <c r="T47" s="5">
         <v>9285</v>
       </c>
-      <c r="T47">
+      <c r="U47" s="5">
         <v>9804</v>
       </c>
-      <c r="U47">
+      <c r="V47" s="5">
         <v>9804</v>
       </c>
-      <c r="V47">
+      <c r="W47" s="5">
         <v>11832</v>
       </c>
-      <c r="W47">
+      <c r="X47" s="5">
         <v>12363</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="6">
+        <v>1502</v>
+      </c>
+      <c r="C48" s="5">
         <v>1757</v>
       </c>
-      <c r="C48">
+      <c r="D48" s="5">
         <v>2021</v>
       </c>
-      <c r="D48">
+      <c r="E48" s="5">
         <v>2275</v>
       </c>
-      <c r="E48">
+      <c r="F48" s="5">
         <v>2717</v>
       </c>
-      <c r="F48">
+      <c r="G48" s="5">
         <v>3066</v>
       </c>
-      <c r="G48">
+      <c r="H48" s="5">
         <v>3753</v>
       </c>
-      <c r="H48">
+      <c r="I48" s="5">
         <v>4344</v>
       </c>
-      <c r="I48">
+      <c r="J48" s="5">
         <v>4746</v>
       </c>
-      <c r="J48">
+      <c r="K48" s="5">
         <v>5437</v>
       </c>
-      <c r="K48">
+      <c r="L48" s="5">
         <v>5718</v>
       </c>
-      <c r="L48">
+      <c r="M48" s="5">
         <v>6169</v>
       </c>
-      <c r="M48">
+      <c r="N48" s="5">
         <v>6905</v>
       </c>
-      <c r="N48">
+      <c r="O48" s="5">
         <v>7641</v>
       </c>
-      <c r="O48">
+      <c r="P48" s="5">
         <v>9276</v>
       </c>
-      <c r="P48">
+      <c r="Q48" s="5">
         <v>9276</v>
       </c>
-      <c r="Q48">
+      <c r="R48" s="5">
         <v>9627</v>
       </c>
-      <c r="R48">
+      <c r="S48" s="5">
         <v>9897</v>
       </c>
-      <c r="S48">
+      <c r="T48" s="5">
         <v>10330</v>
       </c>
-      <c r="T48">
+      <c r="U48" s="5">
         <v>10710</v>
       </c>
-      <c r="U48">
+      <c r="V48" s="5">
         <v>10710</v>
       </c>
-      <c r="V48">
+      <c r="W48" s="5">
         <v>12388</v>
       </c>
-      <c r="W48">
+      <c r="X48" s="5">
         <v>12794</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="6">
+        <v>1446</v>
+      </c>
+      <c r="C49" s="5">
         <v>1727</v>
       </c>
-      <c r="C49">
+      <c r="D49" s="5">
         <v>2085</v>
       </c>
-      <c r="D49">
+      <c r="E49" s="5">
         <v>2355</v>
       </c>
-      <c r="E49">
+      <c r="F49" s="5">
         <v>2738</v>
       </c>
-      <c r="F49">
+      <c r="G49" s="5">
         <v>3255</v>
       </c>
-      <c r="G49">
+      <c r="H49" s="5">
         <v>3865</v>
       </c>
-      <c r="H49">
+      <c r="I49" s="5">
         <v>4713</v>
       </c>
-      <c r="I49">
+      <c r="J49" s="5">
         <v>5040</v>
       </c>
-      <c r="J49">
+      <c r="K49" s="5">
         <v>5688</v>
       </c>
-      <c r="K49">
+      <c r="L49" s="5">
         <v>5950</v>
       </c>
-      <c r="L49">
+      <c r="M49" s="5">
         <v>6579</v>
       </c>
-      <c r="M49">
+      <c r="N49" s="5">
         <v>6488</v>
       </c>
-      <c r="N49">
+      <c r="O49" s="5">
         <v>7454</v>
       </c>
-      <c r="O49">
+      <c r="P49" s="5">
         <v>8382</v>
       </c>
-      <c r="P49">
+      <c r="Q49" s="5">
         <v>8639</v>
       </c>
-      <c r="Q49">
+      <c r="R49" s="5">
         <v>8739</v>
       </c>
-      <c r="R49">
+      <c r="S49" s="5">
         <v>9222</v>
       </c>
-      <c r="S49">
+      <c r="T49" s="5">
         <v>9699</v>
       </c>
-      <c r="T49">
+      <c r="U49" s="5">
         <v>10372</v>
       </c>
-      <c r="U49">
+      <c r="V49" s="5">
         <v>10833</v>
       </c>
-      <c r="V49">
+      <c r="W49" s="5">
         <v>13085</v>
       </c>
-      <c r="W49">
+      <c r="X49" s="5">
         <v>13513</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="4"/>
+      <c r="C50" s="5">
         <v>1666</v>
       </c>
-      <c r="C50">
+      <c r="D50" s="5">
         <v>1856</v>
       </c>
-      <c r="D50">
+      <c r="E50" s="5">
         <v>2059</v>
       </c>
-      <c r="E50">
+      <c r="F50" s="5">
         <v>2431</v>
       </c>
-      <c r="F50">
+      <c r="G50" s="5">
         <v>2734</v>
       </c>
-      <c r="G50">
+      <c r="H50" s="5">
         <v>3442</v>
       </c>
-      <c r="H50">
+      <c r="I50" s="5">
         <v>4033</v>
       </c>
-      <c r="I50">
+      <c r="J50" s="5">
         <v>4445</v>
       </c>
-      <c r="J50">
+      <c r="K50" s="5">
         <v>5132</v>
       </c>
-      <c r="K50">
+      <c r="L50" s="5">
         <v>5345</v>
       </c>
-      <c r="L50">
+      <c r="M50" s="5">
         <v>5783</v>
       </c>
-      <c r="M50">
+      <c r="N50" s="5">
         <v>6131</v>
       </c>
-      <c r="N50">
+      <c r="O50" s="5">
         <v>6971</v>
       </c>
-      <c r="O50">
+      <c r="P50" s="5">
         <v>8053</v>
       </c>
-      <c r="P50">
+      <c r="Q50" s="5">
         <v>8242</v>
       </c>
-      <c r="Q50">
+      <c r="R50" s="5">
         <v>8234</v>
       </c>
-      <c r="R50">
+      <c r="S50" s="5">
         <v>8642</v>
       </c>
-      <c r="S50">
+      <c r="T50" s="5">
         <v>8991</v>
       </c>
-      <c r="T50">
+      <c r="U50" s="5">
         <v>9760</v>
       </c>
-      <c r="U50">
+      <c r="V50" s="5">
         <v>9938</v>
       </c>
-      <c r="V50">
+      <c r="W50" s="5">
         <v>12110</v>
       </c>
-      <c r="W50">
+      <c r="X50" s="5">
         <v>12506</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>49</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="4"/>
+      <c r="C51" s="5">
         <v>1677</v>
       </c>
-      <c r="C51">
+      <c r="D51" s="5">
         <v>1800</v>
       </c>
-      <c r="D51">
+      <c r="E51" s="5">
         <v>2123</v>
       </c>
-      <c r="E51">
+      <c r="F51" s="5">
         <v>2497</v>
       </c>
-      <c r="F51">
+      <c r="G51" s="5">
         <v>2999</v>
       </c>
-      <c r="G51">
+      <c r="H51" s="5">
         <v>3448</v>
       </c>
-      <c r="H51">
+      <c r="I51" s="5">
         <v>4072</v>
       </c>
-      <c r="I51">
+      <c r="J51" s="5">
         <v>4341</v>
       </c>
-      <c r="J51">
+      <c r="K51" s="5">
         <v>5163</v>
       </c>
-      <c r="K51">
+      <c r="L51" s="5">
         <v>5338</v>
       </c>
-      <c r="L51">
+      <c r="M51" s="5">
         <v>5589</v>
       </c>
-      <c r="M51">
+      <c r="N51" s="5">
         <v>6057</v>
       </c>
-      <c r="N51">
+      <c r="O51" s="5">
         <v>6839</v>
       </c>
-      <c r="O51">
+      <c r="P51" s="5">
         <v>8120</v>
       </c>
-      <c r="P51">
+      <c r="Q51" s="5">
         <v>8398</v>
       </c>
-      <c r="Q51">
+      <c r="R51" s="5">
         <v>8326</v>
       </c>
-      <c r="R51">
+      <c r="S51" s="5">
         <v>8774</v>
       </c>
-      <c r="S51">
+      <c r="T51" s="5">
         <v>9179</v>
       </c>
-      <c r="T51">
+      <c r="U51" s="5">
         <v>9610</v>
       </c>
-      <c r="U51">
+      <c r="V51" s="5">
         <v>9610</v>
       </c>
-      <c r="V51">
+      <c r="W51" s="5">
         <v>11692</v>
       </c>
-      <c r="W51">
+      <c r="X51" s="5">
         <v>12075</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>50</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="6">
+        <v>1661</v>
+      </c>
+      <c r="C52" s="5">
         <v>1977</v>
       </c>
-      <c r="C52">
+      <c r="D52" s="5">
         <v>2246</v>
       </c>
-      <c r="D52">
+      <c r="E52" s="5">
         <v>2630</v>
       </c>
-      <c r="E52">
+      <c r="F52" s="5">
         <v>3152</v>
       </c>
-      <c r="F52">
+      <c r="G52" s="5">
         <v>3727</v>
       </c>
-      <c r="G52">
+      <c r="H52" s="5">
         <v>4279</v>
       </c>
-      <c r="H52">
+      <c r="I52" s="5">
         <v>4984</v>
       </c>
-      <c r="I52">
+      <c r="J52" s="5">
         <v>5408</v>
       </c>
-      <c r="J52">
+      <c r="K52" s="5">
         <v>6191</v>
       </c>
-      <c r="K52">
+      <c r="L52" s="5">
         <v>6420</v>
       </c>
-      <c r="L52">
+      <c r="M52" s="5">
         <v>6903</v>
       </c>
-      <c r="M52">
+      <c r="N52" s="5">
         <v>7482</v>
       </c>
-      <c r="N52">
+      <c r="O52" s="5">
         <v>7954</v>
       </c>
-      <c r="O52">
+      <c r="P52" s="5">
         <v>8873</v>
       </c>
-      <c r="P52">
+      <c r="Q52" s="5">
         <v>9664</v>
       </c>
-      <c r="Q52">
+      <c r="R52" s="5">
         <v>9400</v>
       </c>
-      <c r="R52">
+      <c r="S52" s="5">
         <v>9872</v>
       </c>
-      <c r="S52">
+      <c r="T52" s="5">
         <v>10148</v>
       </c>
-      <c r="T52">
+      <c r="U52" s="5">
         <v>10962</v>
       </c>
-      <c r="U52">
+      <c r="V52" s="5">
         <v>10979</v>
       </c>
-      <c r="V52">
+      <c r="W52" s="5">
         <v>13085</v>
       </c>
-      <c r="W52">
+      <c r="X52" s="5">
         <v>13513</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="6">
+        <v>1535</v>
+      </c>
+      <c r="C53" s="5">
         <v>1831</v>
       </c>
-      <c r="C53">
+      <c r="D53" s="5">
         <v>2021</v>
       </c>
-      <c r="D53">
+      <c r="E53" s="5">
         <v>2325</v>
       </c>
-      <c r="E53">
+      <c r="F53" s="5">
         <v>2634</v>
       </c>
-      <c r="F53">
+      <c r="G53" s="5">
         <v>2919</v>
       </c>
-      <c r="G53">
+      <c r="H53" s="5">
         <v>3735</v>
       </c>
-      <c r="H53">
+      <c r="I53" s="5">
         <v>4203</v>
       </c>
-      <c r="I53">
+      <c r="J53" s="5">
         <v>4488</v>
       </c>
-      <c r="J53">
+      <c r="K53" s="5">
         <v>5059</v>
       </c>
-      <c r="K53">
+      <c r="L53" s="5">
         <v>5271</v>
       </c>
-      <c r="L53">
+      <c r="M53" s="5">
         <v>5722</v>
       </c>
-      <c r="M53">
+      <c r="N53" s="5">
         <v>6126</v>
       </c>
-      <c r="N53">
+      <c r="O53" s="5">
         <v>6932</v>
       </c>
-      <c r="O53">
+      <c r="P53" s="5">
         <v>7986</v>
       </c>
-      <c r="P53">
+      <c r="Q53" s="5">
         <v>8168</v>
       </c>
-      <c r="Q53">
+      <c r="R53" s="5">
         <v>8222</v>
       </c>
-      <c r="R53">
+      <c r="S53" s="5">
         <v>8599</v>
       </c>
-      <c r="S53">
+      <c r="T53" s="5">
         <v>8809</v>
       </c>
-      <c r="T53">
+      <c r="U53" s="5">
         <v>9631</v>
       </c>
-      <c r="U53">
+      <c r="V53" s="5">
         <v>9844</v>
       </c>
-      <c r="V53">
+      <c r="W53" s="5">
         <v>11692</v>
       </c>
-      <c r="W53">
+      <c r="X53" s="5">
         <v>12075</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>52</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="6">
+        <v>1367</v>
+      </c>
+      <c r="C54" s="5">
         <v>1702</v>
       </c>
-      <c r="C54">
+      <c r="D54" s="5">
         <v>1875</v>
       </c>
-      <c r="D54">
+      <c r="E54" s="5">
         <v>2276</v>
       </c>
-      <c r="E54">
+      <c r="F54" s="5">
         <v>2530</v>
       </c>
-      <c r="F54">
+      <c r="G54" s="5">
         <v>2936</v>
       </c>
-      <c r="G54">
+      <c r="H54" s="5">
         <v>3507</v>
       </c>
-      <c r="H54">
+      <c r="I54" s="5">
         <v>4074</v>
       </c>
-      <c r="I54">
+      <c r="J54" s="5">
         <v>4414</v>
       </c>
-      <c r="J54">
+      <c r="K54" s="5">
         <v>5164</v>
       </c>
-      <c r="K54">
+      <c r="L54" s="5">
         <v>5432</v>
       </c>
-      <c r="L54">
+      <c r="M54" s="5">
         <v>5786</v>
       </c>
-      <c r="M54">
+      <c r="N54" s="5">
         <v>6472</v>
       </c>
-      <c r="N54">
+      <c r="O54" s="5">
         <v>7298</v>
       </c>
-      <c r="O54">
+      <c r="P54" s="5">
         <v>8528</v>
       </c>
-      <c r="P54">
+      <c r="Q54" s="5">
         <v>8826</v>
       </c>
-      <c r="Q54">
+      <c r="R54" s="5">
         <v>9062</v>
       </c>
-      <c r="R54">
+      <c r="S54" s="5">
         <v>9346</v>
       </c>
-      <c r="S54">
+      <c r="T54" s="5">
         <v>9630</v>
       </c>
-      <c r="T54">
+      <c r="U54" s="5">
         <v>10306</v>
       </c>
-      <c r="U54">
+      <c r="V54" s="5">
         <v>10642</v>
       </c>
-      <c r="V54">
+      <c r="W54" s="5">
         <v>12388</v>
       </c>
-      <c r="W54">
+      <c r="X54" s="5">
         <v>12794</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="6">
+        <v>1496</v>
+      </c>
+      <c r="C55" s="5">
         <v>1816</v>
       </c>
-      <c r="C55">
+      <c r="D55" s="5">
         <v>2081</v>
       </c>
-      <c r="D55">
+      <c r="E55" s="5">
         <v>2313</v>
       </c>
-      <c r="E55">
+      <c r="F55" s="5">
         <v>2630</v>
       </c>
-      <c r="F55">
+      <c r="G55" s="5">
         <v>2977</v>
       </c>
-      <c r="G55">
+      <c r="H55" s="5">
         <v>3509</v>
       </c>
-      <c r="H55">
+      <c r="I55" s="5">
         <v>4249</v>
       </c>
-      <c r="I55">
+      <c r="J55" s="5">
         <v>4589</v>
       </c>
-      <c r="J55">
+      <c r="K55" s="5">
         <v>5238</v>
       </c>
-      <c r="K55">
+      <c r="L55" s="5">
         <v>5570</v>
       </c>
-      <c r="L55">
+      <c r="M55" s="5">
         <v>6041</v>
       </c>
-      <c r="M55">
+      <c r="N55" s="5">
         <v>6509</v>
       </c>
-      <c r="N55">
+      <c r="O55" s="5">
         <v>7605</v>
       </c>
-      <c r="O55">
+      <c r="P55" s="5">
         <v>8793</v>
       </c>
-      <c r="P55">
+      <c r="Q55" s="5">
         <v>9142</v>
       </c>
-      <c r="Q55">
+      <c r="R55" s="5">
         <v>9220</v>
       </c>
-      <c r="R55">
+      <c r="S55" s="5">
         <v>9387</v>
       </c>
-      <c r="S55">
+      <c r="T55" s="5">
         <v>9795</v>
       </c>
-      <c r="T55">
+      <c r="U55" s="5">
         <v>10452</v>
       </c>
-      <c r="U55">
+      <c r="V55" s="5">
         <v>10696</v>
       </c>
-      <c r="V55">
+      <c r="W55" s="5">
         <v>13085</v>
       </c>
-      <c r="W55">
+      <c r="X55" s="5">
         <v>13513</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="6">
+        <v>1703</v>
+      </c>
+      <c r="C56" s="5">
         <v>2034</v>
       </c>
-      <c r="C56">
+      <c r="D56" s="5">
         <v>2173</v>
       </c>
-      <c r="D56">
+      <c r="E56" s="5">
         <v>2432</v>
       </c>
-      <c r="E56">
+      <c r="F56" s="5">
         <v>2861</v>
       </c>
-      <c r="F56">
+      <c r="G56" s="5">
         <v>3324</v>
       </c>
-      <c r="G56">
+      <c r="H56" s="5">
         <v>3902</v>
       </c>
-      <c r="H56">
+      <c r="I56" s="5">
         <v>4714</v>
       </c>
-      <c r="I56">
+      <c r="J56" s="5">
         <v>5201</v>
       </c>
-      <c r="J56">
+      <c r="K56" s="5">
         <v>5946</v>
       </c>
-      <c r="K56">
+      <c r="L56" s="5">
         <v>6513</v>
       </c>
-      <c r="L56">
+      <c r="M56" s="5">
         <v>7005</v>
       </c>
-      <c r="M56">
+      <c r="N56" s="5">
         <v>7238</v>
       </c>
-      <c r="N56">
+      <c r="O56" s="5">
         <v>8025</v>
       </c>
-      <c r="O56">
+      <c r="P56" s="5">
         <v>9670</v>
       </c>
-      <c r="P56">
+      <c r="Q56" s="5">
         <v>9973</v>
       </c>
-      <c r="Q56">
+      <c r="R56" s="5">
         <v>10031</v>
       </c>
-      <c r="R56">
+      <c r="S56" s="5">
         <v>10217</v>
       </c>
-      <c r="S56">
+      <c r="T56" s="5">
         <v>10186</v>
       </c>
-      <c r="T56">
+      <c r="U56" s="5">
         <v>10817</v>
       </c>
-      <c r="U56">
+      <c r="V56" s="5">
         <v>11206</v>
       </c>
-      <c r="V56">
+      <c r="W56" s="5">
         <v>13501</v>
       </c>
-      <c r="W56">
+      <c r="X56" s="5">
         <v>14088</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
-      <c r="D57">
+      <c r="B57" s="4"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5">
         <v>2428</v>
       </c>
-      <c r="E57">
+      <c r="F57" s="5">
         <v>2727</v>
       </c>
-      <c r="F57">
+      <c r="G57" s="5">
         <v>3555</v>
       </c>
-      <c r="G57">
+      <c r="H57" s="5">
         <v>3983</v>
       </c>
-      <c r="H57">
+      <c r="I57" s="5">
         <v>4717</v>
       </c>
-      <c r="I57">
+      <c r="J57" s="5">
         <v>5297</v>
       </c>
-      <c r="J57">
+      <c r="K57" s="5">
         <v>5651</v>
       </c>
-      <c r="K57">
+      <c r="L57" s="5">
         <v>6325</v>
       </c>
-      <c r="L57">
+      <c r="M57" s="5">
         <v>6623</v>
       </c>
-      <c r="M57">
+      <c r="N57" s="5">
         <v>7716</v>
       </c>
-      <c r="N57">
+      <c r="O57" s="5">
         <v>8470</v>
       </c>
-      <c r="O57">
+      <c r="P57" s="5">
         <v>9692</v>
       </c>
-      <c r="P57">
+      <c r="Q57" s="5">
         <v>9855</v>
       </c>
-      <c r="Q57">
+      <c r="R57" s="5">
         <v>10197</v>
       </c>
-      <c r="R57">
+      <c r="S57" s="5">
         <v>10450</v>
       </c>
-      <c r="S57">
+      <c r="T57" s="5">
         <v>11019</v>
       </c>
-      <c r="T57">
+      <c r="U57" s="5">
         <v>14740</v>
       </c>
-      <c r="U57">
+      <c r="V57" s="5">
         <v>11748</v>
       </c>
-      <c r="V57">
+      <c r="W57" s="5">
         <v>13919</v>
       </c>
-      <c r="W57">
+      <c r="X57" s="5">
         <v>14375</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>56</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="4">
+        <v>1620</v>
+      </c>
+      <c r="C58" s="5">
         <v>1833</v>
       </c>
-      <c r="C58">
+      <c r="D58" s="5">
         <v>2046</v>
       </c>
-      <c r="D58">
+      <c r="E58" s="5">
         <v>2303</v>
       </c>
-      <c r="E58">
+      <c r="F58" s="5">
         <v>2571</v>
       </c>
-      <c r="F58">
+      <c r="G58" s="5">
         <v>2939</v>
       </c>
-      <c r="G58">
+      <c r="H58" s="5">
         <v>3578</v>
       </c>
-      <c r="H58">
+      <c r="I58" s="5">
         <v>4320</v>
       </c>
-      <c r="I58">
+      <c r="J58" s="5">
         <v>4595</v>
       </c>
-      <c r="J58">
+      <c r="K58" s="5">
         <v>5234</v>
       </c>
-      <c r="K58">
+      <c r="L58" s="5">
         <v>5552</v>
       </c>
-      <c r="L58">
+      <c r="M58" s="5">
         <v>6149</v>
       </c>
-      <c r="M58">
+      <c r="N58" s="5">
         <v>6936</v>
       </c>
-      <c r="N58">
+      <c r="O58" s="5">
         <v>7944</v>
       </c>
-      <c r="O58">
+      <c r="P58" s="5">
         <v>9038</v>
       </c>
-      <c r="P58">
+      <c r="Q58" s="5">
         <v>8984</v>
       </c>
-      <c r="Q58">
+      <c r="R58" s="5">
         <v>8962</v>
       </c>
-      <c r="R58">
+      <c r="S58" s="5">
         <v>9330</v>
       </c>
-      <c r="S58">
+      <c r="T58" s="5">
         <v>10038</v>
       </c>
-      <c r="T58">
+      <c r="U58" s="5">
         <v>11232</v>
       </c>
-      <c r="U58">
+      <c r="V58" s="5">
         <v>11430</v>
       </c>
-      <c r="V58">
+      <c r="W58" s="5">
         <v>13076</v>
       </c>
-      <c r="W58">
+      <c r="X58" s="5">
         <v>13730</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>57</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="4">
+        <v>1445</v>
+      </c>
+      <c r="C59" s="5">
         <v>1812</v>
       </c>
-      <c r="C59">
+      <c r="D59" s="5">
         <v>2103</v>
       </c>
-      <c r="D59">
+      <c r="E59" s="5">
         <v>2458</v>
       </c>
-      <c r="E59">
+      <c r="F59" s="5">
         <v>3016</v>
       </c>
-      <c r="F59">
+      <c r="G59" s="5">
         <v>3841</v>
       </c>
-      <c r="G59">
+      <c r="H59" s="5">
         <v>4525</v>
       </c>
-      <c r="H59">
+      <c r="I59" s="5">
         <v>5512</v>
       </c>
-      <c r="I59">
+      <c r="J59" s="5">
         <v>6670</v>
       </c>
-      <c r="J59">
+      <c r="K59" s="5">
         <v>5612</v>
       </c>
-      <c r="K59">
+      <c r="L59" s="5">
         <v>5870</v>
       </c>
-      <c r="L59">
+      <c r="M59" s="5">
         <v>6505</v>
       </c>
-      <c r="M59">
+      <c r="N59" s="5">
         <v>6924</v>
       </c>
-      <c r="N59">
+      <c r="O59" s="5">
         <v>8175</v>
       </c>
-      <c r="O59">
+      <c r="P59" s="5">
         <v>9260</v>
       </c>
-      <c r="P59">
+      <c r="Q59" s="5">
         <v>9353</v>
       </c>
-      <c r="Q59">
+      <c r="R59" s="5">
         <v>9405</v>
       </c>
-      <c r="R59">
+      <c r="S59" s="5">
         <v>9752</v>
       </c>
-      <c r="S59">
+      <c r="T59" s="5">
         <v>10041</v>
       </c>
-      <c r="T59">
+      <c r="U59" s="5">
         <v>10697</v>
       </c>
-      <c r="U59">
+      <c r="V59" s="5">
         <v>10838</v>
       </c>
-      <c r="V59">
+      <c r="W59" s="5">
         <v>13085</v>
       </c>
-      <c r="W59">
+      <c r="X59" s="5">
         <v>13513</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="4"/>
+      <c r="C60" s="5">
         <v>2024</v>
       </c>
-      <c r="C60">
+      <c r="D60" s="5">
         <v>2371</v>
       </c>
-      <c r="D60">
+      <c r="E60" s="5">
         <v>2974</v>
       </c>
-      <c r="E60">
+      <c r="F60" s="5">
         <v>3372</v>
       </c>
-      <c r="F60">
+      <c r="G60" s="5">
         <v>4014</v>
       </c>
-      <c r="G60">
+      <c r="H60" s="5">
         <v>4148</v>
       </c>
-      <c r="H60">
+      <c r="I60" s="5">
         <v>4647</v>
       </c>
-      <c r="I60">
+      <c r="J60" s="5">
         <v>4968</v>
       </c>
-      <c r="J60">
+      <c r="K60" s="5">
         <v>5643</v>
       </c>
-      <c r="K60">
+      <c r="L60" s="5">
         <v>6229</v>
       </c>
-      <c r="L60">
+      <c r="M60" s="5">
         <v>6766</v>
       </c>
-      <c r="M60">
+      <c r="N60" s="5">
         <v>7301</v>
       </c>
-      <c r="N60">
+      <c r="O60" s="5">
         <v>8263</v>
       </c>
-      <c r="O60">
+      <c r="P60" s="5">
         <v>9259</v>
       </c>
-      <c r="P60">
+      <c r="Q60" s="5">
         <v>9247</v>
       </c>
-      <c r="Q60">
+      <c r="R60" s="5">
         <v>9563</v>
       </c>
-      <c r="R60">
+      <c r="S60" s="5">
         <v>10395</v>
       </c>
-      <c r="S60">
+      <c r="T60" s="5">
         <v>11274</v>
       </c>
-      <c r="T60">
+      <c r="U60" s="5">
         <v>12333</v>
       </c>
-      <c r="U60">
+      <c r="V60" s="5">
         <v>12810</v>
       </c>
-      <c r="V60">
+      <c r="W60" s="5">
         <v>15172</v>
       </c>
-      <c r="W60">
+      <c r="X60" s="5">
         <v>15669</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>59</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="4"/>
+      <c r="C61" s="5">
         <v>1956</v>
       </c>
-      <c r="C61">
+      <c r="D61" s="5">
         <v>2336</v>
       </c>
-      <c r="D61">
+      <c r="E61" s="5">
         <v>2659</v>
       </c>
-      <c r="E61">
+      <c r="F61" s="5">
         <v>3105</v>
       </c>
-      <c r="F61">
+      <c r="G61" s="5">
         <v>3321</v>
       </c>
-      <c r="G61">
+      <c r="H61" s="5">
         <v>4019</v>
       </c>
-      <c r="H61">
+      <c r="I61" s="5">
         <v>4581</v>
       </c>
-      <c r="I61">
+      <c r="J61" s="5">
         <v>5084</v>
       </c>
-      <c r="J61">
+      <c r="K61" s="5">
         <v>5622</v>
       </c>
-      <c r="K61">
+      <c r="L61" s="5">
         <v>5994</v>
       </c>
-      <c r="L61">
+      <c r="M61" s="5">
         <v>6462</v>
       </c>
-      <c r="M61">
+      <c r="N61" s="5">
         <v>8137</v>
       </c>
-      <c r="N61">
+      <c r="O61" s="5">
         <v>8624</v>
       </c>
-      <c r="O61">
+      <c r="P61" s="5">
         <v>9564</v>
       </c>
-      <c r="P61">
+      <c r="Q61" s="5">
         <v>9775</v>
       </c>
-      <c r="Q61">
+      <c r="R61" s="5">
         <v>9342</v>
       </c>
-      <c r="R61">
+      <c r="S61" s="5">
         <v>9949</v>
       </c>
-      <c r="S61">
+      <c r="T61" s="5">
         <v>10384</v>
       </c>
-      <c r="T61">
+      <c r="U61" s="5">
         <v>10674</v>
       </c>
-      <c r="U61">
+      <c r="V61" s="5">
         <v>11494</v>
       </c>
-      <c r="V61">
+      <c r="W61" s="5">
         <v>14059</v>
       </c>
-      <c r="W61">
+      <c r="X61" s="5">
         <v>14519</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>60</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="6">
+        <v>1703</v>
+      </c>
+      <c r="C62" s="5">
         <v>1949</v>
       </c>
-      <c r="C62">
+      <c r="D62" s="5">
         <v>2169</v>
       </c>
-      <c r="D62">
+      <c r="E62" s="5">
         <v>2464</v>
       </c>
-      <c r="E62">
+      <c r="F62" s="5">
         <v>2899</v>
       </c>
-      <c r="F62">
+      <c r="G62" s="5">
         <v>3275</v>
       </c>
-      <c r="G62">
+      <c r="H62" s="5">
         <v>3723</v>
       </c>
-      <c r="H62">
+      <c r="I62" s="5">
         <v>4448</v>
       </c>
-      <c r="I62">
+      <c r="J62" s="5">
         <v>4890</v>
       </c>
-      <c r="J62">
+      <c r="K62" s="5">
         <v>5434</v>
       </c>
-      <c r="K62">
+      <c r="L62" s="5">
         <v>5895</v>
       </c>
-      <c r="L62">
+      <c r="M62" s="5">
         <v>6405</v>
       </c>
-      <c r="M62">
+      <c r="N62" s="5">
         <v>7101</v>
       </c>
-      <c r="N62">
+      <c r="O62" s="5">
         <v>8006</v>
       </c>
-      <c r="O62">
+      <c r="P62" s="5">
         <v>8905</v>
       </c>
-      <c r="P62">
+      <c r="Q62" s="5">
         <v>8958</v>
       </c>
-      <c r="Q62">
+      <c r="R62" s="5">
         <v>9133</v>
       </c>
-      <c r="R62">
+      <c r="S62" s="5">
         <v>9876</v>
       </c>
-      <c r="S62">
+      <c r="T62" s="5">
         <v>10809</v>
       </c>
-      <c r="T62">
+      <c r="U62" s="5">
         <v>11795</v>
       </c>
-      <c r="U62">
+      <c r="V62" s="5">
         <v>11784</v>
       </c>
-      <c r="V62">
+      <c r="W62" s="5">
         <v>14198</v>
       </c>
-      <c r="W62">
+      <c r="X62" s="5">
         <v>14663</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>61</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="6">
+        <v>1339</v>
+      </c>
+      <c r="C63" s="5">
         <v>1514</v>
       </c>
-      <c r="C63">
+      <c r="D63" s="5">
         <v>1823</v>
       </c>
-      <c r="D63">
+      <c r="E63" s="5">
         <v>2095</v>
       </c>
-      <c r="E63">
+      <c r="F63" s="5">
         <v>2375</v>
       </c>
-      <c r="F63">
+      <c r="G63" s="5">
         <v>3049</v>
       </c>
-      <c r="G63">
+      <c r="H63" s="5">
         <v>3561</v>
       </c>
-      <c r="H63">
+      <c r="I63" s="5">
         <v>4510</v>
       </c>
-      <c r="I63">
+      <c r="J63" s="5">
         <v>5113</v>
       </c>
-      <c r="J63">
+      <c r="K63" s="5">
         <v>5871</v>
       </c>
-      <c r="K63">
+      <c r="L63" s="5">
         <v>5943</v>
       </c>
-      <c r="L63">
+      <c r="M63" s="5">
         <v>6257</v>
       </c>
-      <c r="M63">
+      <c r="N63" s="5">
         <v>6561</v>
       </c>
-      <c r="N63">
+      <c r="O63" s="5">
         <v>7580</v>
       </c>
-      <c r="O63">
+      <c r="P63" s="5">
         <v>8785</v>
       </c>
-      <c r="P63">
+      <c r="Q63" s="5">
         <v>8708</v>
       </c>
-      <c r="Q63">
+      <c r="R63" s="5">
         <v>8657</v>
       </c>
-      <c r="R63">
+      <c r="S63" s="5">
         <v>9334</v>
       </c>
-      <c r="S63">
+      <c r="T63" s="5">
         <v>9704</v>
       </c>
-      <c r="T63">
+      <c r="U63" s="5">
         <v>10211</v>
       </c>
-      <c r="U63">
+      <c r="V63" s="5">
         <v>10665</v>
       </c>
-      <c r="V63">
+      <c r="W63" s="5">
         <v>12388</v>
       </c>
-      <c r="W63">
+      <c r="X63" s="5">
         <v>12794</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="4"/>
+      <c r="C64" s="5">
         <v>2084</v>
       </c>
-      <c r="C64">
+      <c r="D64" s="5">
         <v>2579</v>
       </c>
-      <c r="D64">
+      <c r="E64" s="5">
         <v>2865</v>
       </c>
-      <c r="E64">
+      <c r="F64" s="5">
         <v>3250</v>
       </c>
-      <c r="F64">
+      <c r="G64" s="5">
         <v>3716</v>
       </c>
-      <c r="G64">
+      <c r="H64" s="5">
         <v>4178</v>
       </c>
-      <c r="H64">
+      <c r="I64" s="5">
         <v>5232</v>
       </c>
-      <c r="I64">
+      <c r="J64" s="5">
         <v>5889</v>
       </c>
-      <c r="J64">
+      <c r="K64" s="5">
         <v>6557</v>
       </c>
-      <c r="K64">
+      <c r="L64" s="5">
         <v>7028</v>
       </c>
-      <c r="L64">
+      <c r="M64" s="5">
         <v>7715</v>
       </c>
-      <c r="M64">
+      <c r="N64" s="5">
         <v>8249</v>
       </c>
-      <c r="N64">
+      <c r="O64" s="5">
         <v>9186</v>
       </c>
-      <c r="O64">
+      <c r="P64" s="5">
         <v>10598</v>
       </c>
-      <c r="P64">
+      <c r="Q64" s="5">
         <v>10821</v>
       </c>
-      <c r="Q64">
+      <c r="R64" s="5">
         <v>11043</v>
       </c>
-      <c r="R64">
+      <c r="S64" s="5">
         <v>11642</v>
       </c>
-      <c r="S64">
+      <c r="T64" s="5">
         <v>12290</v>
       </c>
-      <c r="T64">
+      <c r="U64" s="5">
         <v>13053</v>
       </c>
-      <c r="U64">
+      <c r="V64" s="5">
         <v>13409</v>
       </c>
-      <c r="V64">
+      <c r="W64" s="5">
         <v>15451</v>
       </c>
-      <c r="W64">
+      <c r="X64" s="5">
         <v>15956</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="4">
+        <v>1743</v>
+      </c>
+      <c r="C65" s="5">
         <v>2066</v>
       </c>
-      <c r="C65">
+      <c r="D65" s="5">
         <v>2428</v>
       </c>
-      <c r="D65">
+      <c r="E65" s="5">
         <v>2706</v>
       </c>
-      <c r="E65">
+      <c r="F65" s="5">
         <v>2948</v>
       </c>
-      <c r="F65">
+      <c r="G65" s="5">
         <v>3373</v>
       </c>
-      <c r="G65">
+      <c r="H65" s="5">
         <v>3940</v>
       </c>
-      <c r="H65">
+      <c r="I65" s="5">
         <v>4743</v>
       </c>
-      <c r="I65">
+      <c r="J65" s="5">
         <v>5163</v>
       </c>
-      <c r="J65">
+      <c r="K65" s="5">
         <v>5667</v>
       </c>
-      <c r="K65">
+      <c r="L65" s="5">
         <v>6086</v>
       </c>
-      <c r="L65">
+      <c r="M65" s="5">
         <v>6557</v>
       </c>
-      <c r="M65">
+      <c r="N65" s="5">
         <v>7768</v>
       </c>
-      <c r="N65">
+      <c r="O65" s="5">
         <v>8629</v>
       </c>
-      <c r="O65">
+      <c r="P65" s="5">
         <v>9814</v>
       </c>
-      <c r="P65">
+      <c r="Q65" s="5">
         <v>9862</v>
       </c>
-      <c r="Q65">
+      <c r="R65" s="5">
         <v>9825</v>
       </c>
-      <c r="R65">
+      <c r="S65" s="5">
         <v>10698</v>
       </c>
-      <c r="S65">
+      <c r="T65" s="5">
         <v>11365</v>
       </c>
-      <c r="T65">
+      <c r="U65" s="5">
         <v>11982</v>
       </c>
-      <c r="U65">
+      <c r="V65" s="5">
         <v>12243</v>
       </c>
-      <c r="V65">
+      <c r="W65" s="5">
         <v>14754</v>
       </c>
-      <c r="W65">
+      <c r="X65" s="5">
         <v>15238</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>64</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="6">
+        <v>1671</v>
+      </c>
+      <c r="C66" s="5">
         <v>2010</v>
       </c>
-      <c r="C66">
+      <c r="D66" s="5">
         <v>2157</v>
       </c>
-      <c r="D66">
+      <c r="E66" s="5">
         <v>2376</v>
       </c>
-      <c r="E66">
+      <c r="F66" s="5">
         <v>2673</v>
       </c>
-      <c r="F66">
+      <c r="G66" s="5">
         <v>2933</v>
       </c>
-      <c r="G66">
+      <c r="H66" s="5">
         <v>3565</v>
       </c>
-      <c r="H66">
+      <c r="I66" s="5">
         <v>4099</v>
       </c>
-      <c r="I66">
+      <c r="J66" s="5">
         <v>4260</v>
       </c>
-      <c r="J66">
+      <c r="K66" s="5">
         <v>4811</v>
       </c>
-      <c r="K66">
+      <c r="L66" s="5">
         <v>5151</v>
       </c>
-      <c r="L66">
+      <c r="M66" s="5">
         <v>5698</v>
       </c>
-      <c r="M66">
+      <c r="N66" s="5">
         <v>6682</v>
       </c>
-      <c r="N66">
+      <c r="O66" s="5">
         <v>7569</v>
       </c>
-      <c r="O66">
+      <c r="P66" s="5">
         <v>8566</v>
       </c>
-      <c r="P66">
+      <c r="Q66" s="5">
         <v>8748</v>
       </c>
-      <c r="Q66">
+      <c r="R66" s="5">
         <v>8879</v>
       </c>
-      <c r="R66">
+      <c r="S66" s="5">
         <v>9108</v>
       </c>
-      <c r="S66">
+      <c r="T66" s="5">
         <v>9764</v>
       </c>
-      <c r="T66">
+      <c r="U66" s="5">
         <v>10403</v>
       </c>
-      <c r="U66">
+      <c r="V66" s="5">
         <v>10727</v>
       </c>
-      <c r="V66">
+      <c r="W66" s="5">
         <v>12667</v>
       </c>
-      <c r="W66">
+      <c r="X66" s="5">
         <v>13081</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="6">
+        <v>1702</v>
+      </c>
+      <c r="C67" s="5">
         <v>2086</v>
       </c>
-      <c r="C67">
+      <c r="D67" s="5">
         <v>2317</v>
       </c>
-      <c r="D67">
+      <c r="E67" s="5">
         <v>2573</v>
       </c>
-      <c r="E67">
+      <c r="F67" s="5">
         <v>3005</v>
       </c>
-      <c r="F67">
+      <c r="G67" s="5">
         <v>3674</v>
       </c>
-      <c r="G67">
+      <c r="H67" s="5">
         <v>4210</v>
       </c>
-      <c r="H67">
+      <c r="I67" s="5">
         <v>4927</v>
       </c>
-      <c r="I67">
+      <c r="J67" s="5">
         <v>5391</v>
       </c>
-      <c r="J67">
+      <c r="K67" s="5">
         <v>6000</v>
       </c>
-      <c r="K67">
+      <c r="L67" s="5">
         <v>6482</v>
       </c>
-      <c r="L67">
+      <c r="M67" s="5">
         <v>6989</v>
       </c>
-      <c r="M67">
+      <c r="N67" s="5">
         <v>7764</v>
       </c>
-      <c r="N67">
+      <c r="O67" s="5">
         <v>8945</v>
       </c>
-      <c r="O67">
+      <c r="P67" s="5">
         <v>10117</v>
       </c>
-      <c r="P67">
+      <c r="Q67" s="5">
         <v>10225</v>
       </c>
-      <c r="Q67">
+      <c r="R67" s="5">
         <v>10316</v>
       </c>
-      <c r="R67">
+      <c r="S67" s="5">
         <v>10552</v>
       </c>
-      <c r="S67">
+      <c r="T67" s="5">
         <v>11018</v>
       </c>
-      <c r="T67">
+      <c r="U67" s="5">
         <v>11845</v>
       </c>
-      <c r="U67">
+      <c r="V67" s="5">
         <v>12284</v>
       </c>
-      <c r="V67">
+      <c r="W67" s="5">
         <v>14053</v>
       </c>
-      <c r="W67">
+      <c r="X67" s="5">
         <v>14728</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>66</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="6">
+        <v>1439</v>
+      </c>
+      <c r="C68" s="5">
         <v>1782</v>
       </c>
-      <c r="C68">
+      <c r="D68" s="5">
         <v>2012</v>
       </c>
-      <c r="D68">
+      <c r="E68" s="5">
         <v>2153</v>
       </c>
-      <c r="E68">
+      <c r="F68" s="5">
         <v>2898</v>
       </c>
-      <c r="F68">
+      <c r="G68" s="5">
         <v>3375</v>
       </c>
-      <c r="G68">
+      <c r="H68" s="5">
         <v>3929</v>
       </c>
-      <c r="H68">
+      <c r="I68" s="5">
         <v>4528</v>
       </c>
-      <c r="I68">
+      <c r="J68" s="5">
         <v>4869</v>
       </c>
-      <c r="J68">
+      <c r="K68" s="5">
         <v>5028</v>
       </c>
-      <c r="K68">
+      <c r="L68" s="5">
         <v>5258</v>
       </c>
-      <c r="L68">
+      <c r="M68" s="5">
         <v>5773</v>
       </c>
-      <c r="M68">
+      <c r="N68" s="5">
         <v>6302</v>
       </c>
-      <c r="N68">
+      <c r="O68" s="5">
         <v>7253</v>
       </c>
-      <c r="O68">
+      <c r="P68" s="5">
         <v>8338</v>
       </c>
-      <c r="P68">
+      <c r="Q68" s="5">
         <v>8442</v>
       </c>
-      <c r="Q68">
+      <c r="R68" s="5">
         <v>8464</v>
       </c>
-      <c r="R68">
+      <c r="S68" s="5">
         <v>8942</v>
       </c>
-      <c r="S68">
+      <c r="T68" s="5">
         <v>9570</v>
       </c>
-      <c r="T68">
+      <c r="U68" s="5">
         <v>10324</v>
       </c>
-      <c r="U68">
+      <c r="V68" s="5">
         <v>10635</v>
       </c>
-      <c r="V68">
+      <c r="W68" s="5">
         <v>12436</v>
       </c>
-      <c r="W68">
+      <c r="X68" s="5">
         <v>13195</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>67</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="6">
+        <v>1559</v>
+      </c>
+      <c r="C69" s="5">
         <v>1980</v>
       </c>
-      <c r="C69">
+      <c r="D69" s="5">
         <v>2481</v>
       </c>
-      <c r="D69">
+      <c r="E69" s="5">
         <v>2774</v>
       </c>
-      <c r="E69">
+      <c r="F69" s="5">
         <v>3212</v>
       </c>
-      <c r="F69">
+      <c r="G69" s="5">
         <v>3572</v>
       </c>
-      <c r="G69">
+      <c r="H69" s="5">
         <v>4131</v>
       </c>
-      <c r="H69">
+      <c r="I69" s="5">
         <v>4812</v>
       </c>
-      <c r="I69">
+      <c r="J69" s="5">
         <v>5644</v>
       </c>
-      <c r="J69">
+      <c r="K69" s="5">
         <v>6139</v>
       </c>
-      <c r="K69">
+      <c r="L69" s="5">
         <v>6541</v>
       </c>
-      <c r="L69">
+      <c r="M69" s="5">
         <v>7077</v>
       </c>
-      <c r="M69">
+      <c r="N69" s="5">
         <v>7765</v>
       </c>
-      <c r="N69">
+      <c r="O69" s="5">
         <v>8691</v>
       </c>
-      <c r="O69">
+      <c r="P69" s="5">
         <v>10387</v>
       </c>
-      <c r="P69">
+      <c r="Q69" s="5">
         <v>10262</v>
       </c>
-      <c r="Q69">
+      <c r="R69" s="5">
         <v>10379</v>
       </c>
-      <c r="R69">
+      <c r="S69" s="5">
         <v>10595</v>
       </c>
-      <c r="S69">
+      <c r="T69" s="5">
         <v>11140</v>
       </c>
-      <c r="T69">
+      <c r="U69" s="5">
         <v>11850</v>
       </c>
-      <c r="U69">
+      <c r="V69" s="5">
         <v>12218</v>
       </c>
-      <c r="V69">
+      <c r="W69" s="5">
         <v>14004</v>
       </c>
-      <c r="W69">
+      <c r="X69" s="5">
         <v>14466</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>68</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="4"/>
+      <c r="C70" s="5">
         <v>3091</v>
       </c>
-      <c r="C70">
+      <c r="D70" s="5">
         <v>3677</v>
       </c>
-      <c r="D70">
+      <c r="E70" s="5">
         <v>4153</v>
       </c>
-      <c r="E70">
+      <c r="F70" s="5">
         <v>4851</v>
       </c>
-      <c r="F70">
+      <c r="G70" s="5">
         <v>5456</v>
       </c>
-      <c r="G70">
+      <c r="H70" s="5">
         <v>6733</v>
       </c>
-      <c r="H70">
+      <c r="I70" s="5">
         <v>7516</v>
       </c>
-      <c r="I70">
+      <c r="J70" s="5">
         <v>8627</v>
       </c>
-      <c r="J70">
+      <c r="K70" s="5">
         <v>9207</v>
       </c>
-      <c r="K70">
+      <c r="L70" s="5">
         <v>10028</v>
       </c>
-      <c r="L70">
+      <c r="M70" s="5">
         <v>10682</v>
       </c>
-      <c r="M70">
+      <c r="N70" s="5">
         <v>11923</v>
       </c>
-      <c r="N70">
+      <c r="O70" s="5">
         <v>13332</v>
       </c>
-      <c r="O70">
+      <c r="P70" s="5">
         <v>15515</v>
       </c>
-      <c r="P70">
+      <c r="Q70" s="5">
         <v>16080</v>
       </c>
-      <c r="Q70">
+      <c r="R70" s="5">
         <v>16610</v>
       </c>
-      <c r="R70">
+      <c r="S70" s="5">
         <v>16667</v>
       </c>
-      <c r="S70">
+      <c r="T70" s="5">
         <v>17286</v>
       </c>
-      <c r="T70">
+      <c r="U70" s="5">
         <v>17824</v>
       </c>
-      <c r="U70">
+      <c r="V70" s="5">
         <v>18368</v>
       </c>
-      <c r="V70">
+      <c r="W70" s="5">
         <v>21019</v>
       </c>
-      <c r="W70">
+      <c r="X70" s="5">
         <v>21706</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>69</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="4"/>
+      <c r="C71" s="5">
         <v>2603</v>
       </c>
-      <c r="C71">
+      <c r="D71" s="5">
         <v>2924</v>
       </c>
-      <c r="D71">
+      <c r="E71" s="5">
         <v>3259</v>
       </c>
-      <c r="E71">
+      <c r="F71" s="5">
         <v>3970</v>
       </c>
-      <c r="F71">
+      <c r="G71" s="5">
         <v>4423</v>
       </c>
-      <c r="G71">
+      <c r="H71" s="5">
         <v>5111</v>
       </c>
-      <c r="H71">
+      <c r="I71" s="5">
         <v>6071</v>
       </c>
-      <c r="I71">
+      <c r="J71" s="5">
         <v>6401</v>
       </c>
-      <c r="J71">
+      <c r="K71" s="5">
         <v>6865</v>
       </c>
-      <c r="K71">
+      <c r="L71" s="5">
         <v>7336</v>
       </c>
-      <c r="L71">
+      <c r="M71" s="5">
         <v>7839</v>
       </c>
-      <c r="M71">
+      <c r="N71" s="5">
         <v>9649</v>
       </c>
-      <c r="N71">
+      <c r="O71" s="5">
         <v>10683</v>
       </c>
-      <c r="O71">
+      <c r="P71" s="5">
         <v>12535</v>
       </c>
-      <c r="P71">
+      <c r="Q71" s="5">
         <v>12456</v>
       </c>
-      <c r="Q71">
+      <c r="R71" s="5">
         <v>12158</v>
       </c>
-      <c r="R71">
+      <c r="S71" s="5">
         <v>12623</v>
       </c>
-      <c r="S71">
+      <c r="T71" s="5">
         <v>13270</v>
       </c>
-      <c r="T71">
+      <c r="U71" s="5">
         <v>14025</v>
       </c>
-      <c r="U71">
+      <c r="V71" s="5">
         <v>13963</v>
       </c>
-      <c r="V71">
+      <c r="W71" s="5">
         <v>16564</v>
       </c>
-      <c r="W71">
+      <c r="X71" s="5">
         <v>17106</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>70</v>
       </c>
-      <c r="C72">
+      <c r="B72" s="4"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5">
         <v>3092</v>
       </c>
-      <c r="D72">
+      <c r="E72" s="5">
         <v>3662</v>
       </c>
-      <c r="E72">
+      <c r="F72" s="5">
         <v>4331</v>
       </c>
-      <c r="F72">
+      <c r="G72" s="5">
         <v>4854</v>
       </c>
-      <c r="G72">
+      <c r="H72" s="5">
         <v>5443</v>
       </c>
-      <c r="H72">
+      <c r="I72" s="5">
         <v>6902</v>
       </c>
-      <c r="I72">
+      <c r="J72" s="5">
         <v>7993</v>
       </c>
-      <c r="J72">
+      <c r="K72" s="5">
         <v>8676</v>
       </c>
-      <c r="K72">
+      <c r="L72" s="5">
         <v>9039</v>
       </c>
-      <c r="L72">
+      <c r="M72" s="5">
         <v>9482</v>
       </c>
-      <c r="M72">
+      <c r="N72" s="5">
         <v>10182</v>
       </c>
-      <c r="N72">
+      <c r="O72" s="5">
         <v>11495</v>
       </c>
-      <c r="O72">
+      <c r="P72" s="5">
         <v>13427</v>
       </c>
-      <c r="P72">
+      <c r="Q72" s="5">
         <v>12910</v>
       </c>
-      <c r="Q72">
+      <c r="R72" s="5">
         <v>12954</v>
       </c>
-      <c r="R72">
+      <c r="S72" s="5">
         <v>13497</v>
       </c>
-      <c r="S72">
+      <c r="T72" s="5">
         <v>14417</v>
       </c>
-      <c r="T72">
+      <c r="U72" s="5">
         <v>15569</v>
       </c>
-      <c r="U72">
+      <c r="V72" s="5">
         <v>16222</v>
       </c>
-      <c r="V72">
+      <c r="W72" s="5">
         <v>18558</v>
       </c>
-      <c r="W72">
+      <c r="X72" s="5">
         <v>19170</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>71</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="4">
+        <v>1889</v>
+      </c>
+      <c r="C73" s="5">
         <v>2209</v>
       </c>
-      <c r="C73">
+      <c r="D73" s="5">
         <v>2636</v>
       </c>
-      <c r="D73">
+      <c r="E73" s="5">
         <v>3091</v>
       </c>
-      <c r="E73">
+      <c r="F73" s="5">
         <v>3771</v>
       </c>
-      <c r="F73">
+      <c r="G73" s="5">
         <v>4353</v>
       </c>
-      <c r="G73">
+      <c r="H73" s="5">
         <v>5026</v>
       </c>
-      <c r="H73">
+      <c r="I73" s="5">
         <v>5688</v>
       </c>
-      <c r="I73">
+      <c r="J73" s="5">
         <v>6402</v>
       </c>
-      <c r="J73">
+      <c r="K73" s="5">
         <v>7163</v>
       </c>
-      <c r="K73">
+      <c r="L73" s="5">
         <v>7950</v>
       </c>
-      <c r="L73">
+      <c r="M73" s="5">
         <v>8369</v>
       </c>
-      <c r="M73">
+      <c r="N73" s="5">
         <v>9251</v>
       </c>
-      <c r="N73">
+      <c r="O73" s="5">
         <v>9539</v>
       </c>
-      <c r="O73">
+      <c r="P73" s="5">
         <v>11555</v>
       </c>
-      <c r="P73">
+      <c r="Q73" s="5">
         <v>11374</v>
       </c>
-      <c r="Q73">
+      <c r="R73" s="5">
         <v>11203</v>
       </c>
-      <c r="R73">
+      <c r="S73" s="5">
         <v>11172</v>
       </c>
-      <c r="S73">
+      <c r="T73" s="5">
         <v>12379</v>
       </c>
-      <c r="T73">
+      <c r="U73" s="5">
         <v>13530</v>
       </c>
-      <c r="U73">
+      <c r="V73" s="5">
         <v>14017</v>
       </c>
-      <c r="V73">
+      <c r="W73" s="5">
         <v>16174</v>
       </c>
-      <c r="W73">
+      <c r="X73" s="5">
         <v>17047</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>72</v>
       </c>
-      <c r="C74">
+      <c r="B74" s="4"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5">
         <v>3562</v>
       </c>
-      <c r="D74">
+      <c r="E74" s="5">
         <v>4008</v>
       </c>
-      <c r="E74">
+      <c r="F74" s="5">
         <v>4756</v>
       </c>
-      <c r="F74">
+      <c r="G74" s="5">
         <v>5329</v>
       </c>
-      <c r="G74">
+      <c r="H74" s="5">
         <v>6276</v>
       </c>
-      <c r="H74">
+      <c r="I74" s="5">
         <v>7506</v>
       </c>
-      <c r="I74">
+      <c r="J74" s="5">
         <v>8638</v>
       </c>
-      <c r="J74">
+      <c r="K74" s="5">
         <v>9236</v>
       </c>
-      <c r="K74">
+      <c r="L74" s="5">
         <v>10249</v>
       </c>
-      <c r="L74">
+      <c r="M74" s="5">
         <v>11001</v>
       </c>
-      <c r="M74">
+      <c r="N74" s="5">
         <v>14084</v>
       </c>
-      <c r="N74">
+      <c r="O74" s="5">
         <v>15415</v>
       </c>
-      <c r="O74">
+      <c r="P74" s="5">
         <v>17469</v>
       </c>
-      <c r="P74">
+      <c r="Q74" s="5">
         <v>17764</v>
       </c>
-      <c r="Q74">
+      <c r="R74" s="5">
         <v>17635</v>
       </c>
-      <c r="R74">
+      <c r="S74" s="5">
         <v>18910</v>
       </c>
-      <c r="S74">
+      <c r="T74" s="5">
         <v>19695</v>
       </c>
-      <c r="T74">
+      <c r="U74" s="5">
         <v>20830</v>
       </c>
-      <c r="U74">
+      <c r="V74" s="5">
         <v>21102</v>
       </c>
-      <c r="V74">
+      <c r="W74" s="5">
         <v>24220</v>
       </c>
-      <c r="W74">
+      <c r="X74" s="5">
         <v>25013</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>73</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="4"/>
+      <c r="C75" s="5">
         <v>3351</v>
       </c>
-      <c r="C75">
+      <c r="D75" s="5">
         <v>3887</v>
       </c>
-      <c r="D75">
+      <c r="E75" s="5">
         <v>4435</v>
       </c>
-      <c r="E75">
+      <c r="F75" s="5">
         <v>5118</v>
       </c>
-      <c r="F75">
+      <c r="G75" s="5">
         <v>5974</v>
       </c>
-      <c r="G75">
+      <c r="H75" s="5">
         <v>6606</v>
       </c>
-      <c r="H75">
+      <c r="I75" s="5">
         <v>7531</v>
       </c>
-      <c r="I75">
+      <c r="J75" s="5">
         <v>8362</v>
       </c>
-      <c r="J75">
+      <c r="K75" s="5">
         <v>9084</v>
       </c>
-      <c r="K75">
+      <c r="L75" s="5">
         <v>9864</v>
       </c>
-      <c r="L75">
+      <c r="M75" s="5">
         <v>10034</v>
       </c>
-      <c r="M75">
+      <c r="N75" s="5">
         <v>11083</v>
       </c>
-      <c r="N75">
+      <c r="O75" s="5">
         <v>12213</v>
       </c>
-      <c r="O75">
+      <c r="P75" s="5">
         <v>13533</v>
       </c>
-      <c r="P75">
+      <c r="Q75" s="5">
         <v>13728</v>
       </c>
-      <c r="Q75">
+      <c r="R75" s="5">
         <v>13329</v>
       </c>
-      <c r="R75">
+      <c r="S75" s="5">
         <v>14072</v>
       </c>
-      <c r="S75">
+      <c r="T75" s="5">
         <v>14898</v>
       </c>
-      <c r="T75">
+      <c r="U75" s="5">
         <v>16130</v>
       </c>
-      <c r="U75">
+      <c r="V75" s="5">
         <v>15906</v>
       </c>
-      <c r="V75">
+      <c r="W75" s="5">
         <v>18930</v>
       </c>
-      <c r="W75">
+      <c r="X75" s="5">
         <v>19550</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>74</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="4">
+        <v>1799</v>
+      </c>
+      <c r="C76" s="5">
         <v>2200</v>
       </c>
-      <c r="C76">
+      <c r="D76" s="5">
         <v>2593</v>
       </c>
-      <c r="D76">
+      <c r="E76" s="5">
         <v>2940</v>
       </c>
-      <c r="E76">
+      <c r="F76" s="5">
         <v>3594</v>
       </c>
-      <c r="F76">
+      <c r="G76" s="5">
         <v>3894</v>
       </c>
-      <c r="G76">
+      <c r="H76" s="5">
         <v>4674</v>
       </c>
-      <c r="H76">
+      <c r="I76" s="5">
         <v>5386</v>
       </c>
-      <c r="I76">
+      <c r="J76" s="5">
         <v>6116</v>
       </c>
-      <c r="J76">
+      <c r="K76" s="5">
         <v>6752</v>
       </c>
-      <c r="K76">
+      <c r="L76" s="5">
         <v>7394</v>
       </c>
-      <c r="L76">
+      <c r="M76" s="5">
         <v>8252</v>
       </c>
-      <c r="M76">
+      <c r="N76" s="5">
         <v>9532</v>
       </c>
-      <c r="N76">
+      <c r="O76" s="5">
         <v>10870</v>
       </c>
-      <c r="O76">
+      <c r="P76" s="5">
         <v>12228</v>
       </c>
-      <c r="P76">
+      <c r="Q76" s="5">
         <v>12574</v>
       </c>
-      <c r="Q76">
+      <c r="R76" s="5">
         <v>12161</v>
       </c>
-      <c r="R76">
+      <c r="S76" s="5">
         <v>13051</v>
       </c>
-      <c r="S76">
+      <c r="T76" s="5">
         <v>14329</v>
       </c>
-      <c r="T76">
+      <c r="U76" s="5">
         <v>15416</v>
       </c>
-      <c r="U76">
+      <c r="V76" s="5">
         <v>16386</v>
       </c>
-      <c r="V76">
+      <c r="W76" s="5">
         <v>18758</v>
       </c>
-      <c r="W76">
+      <c r="X76" s="5">
         <v>19377</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
-      </c>
-      <c r="N77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5">
         <v>13571</v>
       </c>
-      <c r="O77">
+      <c r="P77" s="5">
         <v>16845</v>
       </c>
-      <c r="P77">
+      <c r="Q77" s="5">
         <v>17775</v>
       </c>
-      <c r="Q77">
+      <c r="R77" s="5">
         <v>20149</v>
       </c>
-      <c r="R77">
+      <c r="S77" s="5">
         <v>21606</v>
       </c>
-      <c r="S77">
+      <c r="T77" s="5">
         <v>22098</v>
       </c>
-      <c r="T77">
+      <c r="U77" s="5">
         <v>23999</v>
       </c>
-      <c r="U77">
+      <c r="V77" s="5">
         <v>24164</v>
       </c>
-      <c r="V77">
+      <c r="W77" s="5">
         <v>31736</v>
       </c>
-      <c r="W77">
+      <c r="X77" s="5">
         <v>35938</v>
       </c>
     </row>
-    <row r="104" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G104" s="2"/>
     </row>
-    <row r="105" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G105" s="2"/>
     </row>
-    <row r="106" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="D106" s="1" t="s">
         <v>11</v>
       </c>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="4:7" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="4:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="G112" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>